--- a/V4.xlsx
+++ b/V4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DE\sem 5\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6083B5C3-EC14-405E-8CF4-F5504C81CB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196115DC-A026-44A9-A15D-DA67169FF645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{7DCB483B-EADE-468B-A11D-0B02376EF2F9}"/>
+    <workbookView xWindow="-23148" yWindow="-756" windowWidth="23256" windowHeight="12576" xr2:uid="{7DCB483B-EADE-468B-A11D-0B02376EF2F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="45">
   <si>
     <t>Si 14</t>
   </si>
@@ -169,6 +169,9 @@
   <si>
     <t>strain_t</t>
   </si>
+  <si>
+    <t>Rm</t>
+  </si>
 </sst>
 </file>
 
@@ -213,7 +216,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -249,11 +252,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -283,6 +297,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -617,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C104F5-0E4C-4247-9FBD-FDB2733B4479}">
-  <dimension ref="A1:X371"/>
+  <dimension ref="A1:Y371"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="16.25" customWidth="1"/>
@@ -628,7 +643,7 @@
     <col min="20" max="20" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="9" customFormat="1">
+    <row r="1" spans="1:25" s="9" customFormat="1">
       <c r="A1" s="9" t="s">
         <v>11</v>
       </c>
@@ -701,8 +716,11 @@
       <c r="X1" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" ht="15.75">
+      <c r="Y1" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -768,8 +786,11 @@
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
-    </row>
-    <row r="3" spans="1:24" ht="15.75">
+      <c r="Y2">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -835,8 +856,11 @@
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
-    </row>
-    <row r="4" spans="1:24" ht="15.75">
+      <c r="Y3">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -902,8 +926,11 @@
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
       <c r="X4" s="6"/>
-    </row>
-    <row r="5" spans="1:24" ht="15.75">
+      <c r="Y4">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -969,8 +996,11 @@
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
       <c r="X5" s="6"/>
-    </row>
-    <row r="6" spans="1:24" ht="15.75">
+      <c r="Y5">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -1036,8 +1066,11 @@
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
       <c r="X6" s="6"/>
-    </row>
-    <row r="7" spans="1:24" ht="15.75">
+      <c r="Y6">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -1103,8 +1136,11 @@
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
       <c r="X7" s="6"/>
-    </row>
-    <row r="8" spans="1:24" ht="15.75">
+      <c r="Y7">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -1170,8 +1206,11 @@
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
       <c r="X8" s="6"/>
-    </row>
-    <row r="9" spans="1:24" ht="15.75">
+      <c r="Y8">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -1237,8 +1276,11 @@
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
-    </row>
-    <row r="10" spans="1:24" ht="15.75">
+      <c r="Y9">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" s="3">
         <v>1</v>
       </c>
@@ -1304,8 +1346,11 @@
       <c r="V10" s="6"/>
       <c r="W10" s="6"/>
       <c r="X10" s="6"/>
-    </row>
-    <row r="11" spans="1:24" ht="15.75">
+      <c r="Y10">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -1371,8 +1416,11 @@
       <c r="V11" s="6"/>
       <c r="W11" s="6"/>
       <c r="X11" s="6"/>
-    </row>
-    <row r="12" spans="1:24" ht="15.75">
+      <c r="Y11">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="15.75">
       <c r="A12" s="3">
         <v>1</v>
       </c>
@@ -1438,8 +1486,11 @@
       <c r="V12" s="6"/>
       <c r="W12" s="6"/>
       <c r="X12" s="6"/>
-    </row>
-    <row r="13" spans="1:24" ht="15.75">
+      <c r="Y12">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="15.75">
       <c r="A13" s="3">
         <v>1</v>
       </c>
@@ -1505,8 +1556,11 @@
       <c r="V13" s="6"/>
       <c r="W13" s="6"/>
       <c r="X13" s="6"/>
-    </row>
-    <row r="14" spans="1:24" ht="15.75">
+      <c r="Y13">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="15.75">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1572,8 +1626,11 @@
       <c r="V14" s="6"/>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
-    </row>
-    <row r="15" spans="1:24" ht="15.75">
+      <c r="Y14">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="15.75">
       <c r="A15" s="3">
         <v>1</v>
       </c>
@@ -1639,8 +1696,11 @@
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
       <c r="X15" s="6"/>
-    </row>
-    <row r="16" spans="1:24" ht="15.75">
+      <c r="Y15">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="15.75">
       <c r="A16" s="3">
         <v>1</v>
       </c>
@@ -1706,8 +1766,11 @@
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
       <c r="X16" s="6"/>
-    </row>
-    <row r="17" spans="1:24" ht="15.75">
+      <c r="Y16">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="15.75">
       <c r="A17" s="3">
         <v>1</v>
       </c>
@@ -1773,8 +1836,11 @@
       <c r="V17" s="6"/>
       <c r="W17" s="6"/>
       <c r="X17" s="6"/>
-    </row>
-    <row r="18" spans="1:24" ht="15.75">
+      <c r="Y17">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="15.75">
       <c r="A18" s="3">
         <v>1</v>
       </c>
@@ -1840,8 +1906,11 @@
       <c r="V18" s="6"/>
       <c r="W18" s="6"/>
       <c r="X18" s="6"/>
-    </row>
-    <row r="19" spans="1:24" ht="15.75">
+      <c r="Y18">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="15.75">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -1907,8 +1976,11 @@
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
       <c r="X19" s="6"/>
-    </row>
-    <row r="20" spans="1:24" ht="15.75">
+      <c r="Y19">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="15.75">
       <c r="A20" s="3">
         <v>1</v>
       </c>
@@ -1974,8 +2046,11 @@
       <c r="V20" s="6"/>
       <c r="W20" s="6"/>
       <c r="X20" s="6"/>
-    </row>
-    <row r="21" spans="1:24" ht="15.75">
+      <c r="Y20">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="15.75">
       <c r="A21" s="3">
         <v>1</v>
       </c>
@@ -2041,8 +2116,11 @@
       <c r="V21" s="6"/>
       <c r="W21" s="6"/>
       <c r="X21" s="6"/>
-    </row>
-    <row r="22" spans="1:24" ht="15.75">
+      <c r="Y21">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="15.75">
       <c r="A22" s="3">
         <v>1</v>
       </c>
@@ -2108,8 +2186,11 @@
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
       <c r="X22" s="6"/>
-    </row>
-    <row r="23" spans="1:24" ht="15.75">
+      <c r="Y22">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="15.75">
       <c r="A23" s="3">
         <v>1</v>
       </c>
@@ -2181,8 +2262,11 @@
       <c r="X23" s="6">
         <v>0.84202999999999995</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" ht="15.75">
+      <c r="Y23">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="15.75">
       <c r="A24" s="3">
         <v>1</v>
       </c>
@@ -2254,8 +2338,11 @@
       <c r="X24" s="6">
         <v>1.0023</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" ht="15.75">
+      <c r="Y24">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="15.75">
       <c r="A25" s="3">
         <v>1</v>
       </c>
@@ -2327,8 +2414,11 @@
       <c r="X25" s="6">
         <v>0.64802999999999999</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" ht="15.75">
+      <c r="Y25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="15.75">
       <c r="A26" s="3">
         <v>1</v>
       </c>
@@ -2400,8 +2490,11 @@
       <c r="X26" s="6">
         <v>0.70604</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" ht="15.75">
+      <c r="Y26">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="15.75">
       <c r="A27" s="3">
         <v>1</v>
       </c>
@@ -2473,8 +2566,11 @@
       <c r="X27" s="6">
         <v>0.38153999999999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" ht="15.75">
+      <c r="Y27">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" ht="15.75">
       <c r="A28" s="3">
         <v>1</v>
       </c>
@@ -2546,8 +2642,11 @@
       <c r="X28" s="6">
         <v>0.41777999999999998</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" ht="15.75">
+      <c r="Y28">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" ht="15.75">
       <c r="A29" s="3">
         <v>1</v>
       </c>
@@ -2619,8 +2718,11 @@
       <c r="X29" s="6">
         <v>0.59501000000000004</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" ht="15.75">
+      <c r="Y29">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="15.75">
       <c r="A30" s="3">
         <v>1</v>
       </c>
@@ -2692,8 +2794,11 @@
       <c r="X30" s="6">
         <v>0.54501999999999995</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" ht="15.75">
+      <c r="Y30">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="15.75">
       <c r="A31" s="3">
         <v>1</v>
       </c>
@@ -2765,8 +2870,11 @@
       <c r="X31" s="6">
         <v>0.50004999999999999</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" ht="15.75">
+      <c r="Y31">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="15.75">
       <c r="A32" s="3">
         <v>1</v>
       </c>
@@ -2838,8 +2946,11 @@
       <c r="X32" s="6">
         <v>0.35482999999999998</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" ht="15.75">
+      <c r="Y32">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" ht="15.75">
       <c r="A33" s="3">
         <v>1</v>
       </c>
@@ -2911,8 +3022,11 @@
       <c r="X33" s="6">
         <v>0.32401000000000002</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" ht="15.75">
+      <c r="Y33">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" ht="15.75">
       <c r="A34" s="3">
         <v>1</v>
       </c>
@@ -2984,8 +3098,11 @@
       <c r="X34" s="6">
         <v>0.27300000000000002</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" ht="15.75">
+      <c r="Y34">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" ht="15.75">
       <c r="A35" s="3">
         <v>1</v>
       </c>
@@ -3057,8 +3174,11 @@
       <c r="X35" s="6">
         <v>0.29722999999999999</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" ht="15.75">
+      <c r="Y35" s="13">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="15.75">
       <c r="A36" s="3">
         <v>2</v>
       </c>
@@ -3124,8 +3244,11 @@
       <c r="V36" s="6"/>
       <c r="W36" s="6"/>
       <c r="X36" s="6"/>
-    </row>
-    <row r="37" spans="1:24" ht="15.75">
+      <c r="Y36" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" ht="15.75">
       <c r="A37" s="3">
         <v>2</v>
       </c>
@@ -3191,8 +3314,11 @@
       <c r="V37" s="6"/>
       <c r="W37" s="6"/>
       <c r="X37" s="6"/>
-    </row>
-    <row r="38" spans="1:24" ht="15.75">
+      <c r="Y37" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="15.75">
       <c r="A38" s="3">
         <v>2</v>
       </c>
@@ -3258,8 +3384,11 @@
       <c r="V38" s="6"/>
       <c r="W38" s="6"/>
       <c r="X38" s="6"/>
-    </row>
-    <row r="39" spans="1:24" ht="15.75">
+      <c r="Y38" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" ht="15.75">
       <c r="A39" s="3">
         <v>2</v>
       </c>
@@ -3325,8 +3454,11 @@
       <c r="V39" s="6"/>
       <c r="W39" s="6"/>
       <c r="X39" s="6"/>
-    </row>
-    <row r="40" spans="1:24" ht="15.75">
+      <c r="Y39" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" ht="15.75">
       <c r="A40" s="3">
         <v>2</v>
       </c>
@@ -3392,8 +3524,11 @@
       <c r="V40" s="6"/>
       <c r="W40" s="6"/>
       <c r="X40" s="6"/>
-    </row>
-    <row r="41" spans="1:24" ht="15.75">
+      <c r="Y40" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" ht="15.75">
       <c r="A41" s="3">
         <v>2</v>
       </c>
@@ -3459,8 +3594,11 @@
       <c r="V41" s="6"/>
       <c r="W41" s="6"/>
       <c r="X41" s="6"/>
-    </row>
-    <row r="42" spans="1:24" ht="15.75">
+      <c r="Y41" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" ht="15.75">
       <c r="A42" s="3">
         <v>2</v>
       </c>
@@ -3526,8 +3664,11 @@
       <c r="V42" s="6"/>
       <c r="W42" s="6"/>
       <c r="X42" s="6"/>
-    </row>
-    <row r="43" spans="1:24" ht="15.75">
+      <c r="Y42" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" ht="15.75">
       <c r="A43" s="3">
         <v>2</v>
       </c>
@@ -3593,8 +3734,11 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6"/>
-    </row>
-    <row r="44" spans="1:24" ht="15.75">
+      <c r="Y43" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" ht="15.75">
       <c r="A44" s="3">
         <v>2</v>
       </c>
@@ -3660,8 +3804,11 @@
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
       <c r="X44" s="6"/>
-    </row>
-    <row r="45" spans="1:24" ht="15.75">
+      <c r="Y44" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" ht="15.75">
       <c r="A45" s="3">
         <v>2</v>
       </c>
@@ -3727,8 +3874,11 @@
       <c r="V45" s="6"/>
       <c r="W45" s="6"/>
       <c r="X45" s="6"/>
-    </row>
-    <row r="46" spans="1:24" ht="15.75">
+      <c r="Y45" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" ht="15.75">
       <c r="A46" s="3">
         <v>2</v>
       </c>
@@ -3794,8 +3944,11 @@
       <c r="V46" s="6"/>
       <c r="W46" s="6"/>
       <c r="X46" s="6"/>
-    </row>
-    <row r="47" spans="1:24" ht="15.75">
+      <c r="Y46" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" ht="15.75">
       <c r="A47" s="3">
         <v>2</v>
       </c>
@@ -3861,8 +4014,11 @@
       <c r="V47" s="6"/>
       <c r="W47" s="6"/>
       <c r="X47" s="6"/>
-    </row>
-    <row r="48" spans="1:24" ht="15.75">
+      <c r="Y47" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" ht="15.75">
       <c r="A48" s="3">
         <v>2</v>
       </c>
@@ -3928,8 +4084,11 @@
       <c r="V48" s="6"/>
       <c r="W48" s="6"/>
       <c r="X48" s="6"/>
-    </row>
-    <row r="49" spans="1:24" ht="15.75">
+      <c r="Y48" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" ht="15.75">
       <c r="A49" s="3">
         <v>2</v>
       </c>
@@ -3995,8 +4154,11 @@
       <c r="V49" s="6"/>
       <c r="W49" s="6"/>
       <c r="X49" s="6"/>
-    </row>
-    <row r="50" spans="1:24" ht="15.75">
+      <c r="Y49" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" ht="15.75">
       <c r="A50" s="3">
         <v>2</v>
       </c>
@@ -4062,8 +4224,11 @@
       <c r="V50" s="6"/>
       <c r="W50" s="6"/>
       <c r="X50" s="6"/>
-    </row>
-    <row r="51" spans="1:24" ht="15.75">
+      <c r="Y50" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" ht="15.75">
       <c r="A51" s="3">
         <v>2</v>
       </c>
@@ -4129,8 +4294,11 @@
       <c r="V51" s="6"/>
       <c r="W51" s="6"/>
       <c r="X51" s="6"/>
-    </row>
-    <row r="52" spans="1:24" ht="15.75">
+      <c r="Y51" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" ht="15.75">
       <c r="A52" s="3">
         <v>2</v>
       </c>
@@ -4196,8 +4364,11 @@
       <c r="V52" s="6"/>
       <c r="W52" s="6"/>
       <c r="X52" s="6"/>
-    </row>
-    <row r="53" spans="1:24" ht="15.75">
+      <c r="Y52" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" ht="15.75">
       <c r="A53" s="3">
         <v>2</v>
       </c>
@@ -4263,8 +4434,11 @@
       <c r="V53" s="6"/>
       <c r="W53" s="6"/>
       <c r="X53" s="6"/>
-    </row>
-    <row r="54" spans="1:24" ht="15.75">
+      <c r="Y53" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" ht="15.75">
       <c r="A54" s="3">
         <v>2</v>
       </c>
@@ -4330,8 +4504,11 @@
       <c r="V54" s="6"/>
       <c r="W54" s="6"/>
       <c r="X54" s="6"/>
-    </row>
-    <row r="55" spans="1:24" ht="15.75">
+      <c r="Y54" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" ht="15.75">
       <c r="A55" s="3">
         <v>2</v>
       </c>
@@ -4397,8 +4574,11 @@
       <c r="V55" s="6"/>
       <c r="W55" s="6"/>
       <c r="X55" s="6"/>
-    </row>
-    <row r="56" spans="1:24" ht="15.75">
+      <c r="Y55" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" ht="15.75">
       <c r="A56" s="3">
         <v>2</v>
       </c>
@@ -4464,8 +4644,11 @@
       <c r="V56" s="6"/>
       <c r="W56" s="6"/>
       <c r="X56" s="6"/>
-    </row>
-    <row r="57" spans="1:24" ht="15.75">
+      <c r="Y56" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" ht="15.75">
       <c r="A57" s="3">
         <v>2</v>
       </c>
@@ -4531,8 +4714,11 @@
       <c r="V57" s="6"/>
       <c r="W57" s="6"/>
       <c r="X57" s="6"/>
-    </row>
-    <row r="58" spans="1:24" ht="15.75">
+      <c r="Y57" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" ht="15.75">
       <c r="A58" s="3">
         <v>2</v>
       </c>
@@ -4598,8 +4784,11 @@
       <c r="V58" s="6"/>
       <c r="W58" s="6"/>
       <c r="X58" s="6"/>
-    </row>
-    <row r="59" spans="1:24" ht="15.75">
+      <c r="Y58" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" ht="15.75">
       <c r="A59" s="3">
         <v>2</v>
       </c>
@@ -4665,8 +4854,11 @@
       <c r="V59" s="6"/>
       <c r="W59" s="6"/>
       <c r="X59" s="6"/>
-    </row>
-    <row r="60" spans="1:24" ht="15.75">
+      <c r="Y59" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" ht="15.75">
       <c r="A60" s="3">
         <v>2</v>
       </c>
@@ -4732,8 +4924,11 @@
       <c r="V60" s="6"/>
       <c r="W60" s="6"/>
       <c r="X60" s="6"/>
-    </row>
-    <row r="61" spans="1:24" ht="15.75">
+      <c r="Y60" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" ht="15.75">
       <c r="A61" s="3">
         <v>2</v>
       </c>
@@ -4799,8 +4994,11 @@
       <c r="V61" s="6"/>
       <c r="W61" s="6"/>
       <c r="X61" s="6"/>
-    </row>
-    <row r="62" spans="1:24" ht="15.75">
+      <c r="Y61" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" ht="15.75">
       <c r="A62" s="3">
         <v>2</v>
       </c>
@@ -4866,8 +5064,11 @@
       <c r="V62" s="6"/>
       <c r="W62" s="6"/>
       <c r="X62" s="6"/>
-    </row>
-    <row r="63" spans="1:24" ht="15.75">
+      <c r="Y62" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" ht="15.75">
       <c r="A63" s="3">
         <v>2</v>
       </c>
@@ -4933,8 +5134,11 @@
       <c r="V63" s="6"/>
       <c r="W63" s="6"/>
       <c r="X63" s="6"/>
-    </row>
-    <row r="64" spans="1:24" ht="15.75">
+      <c r="Y63" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" ht="15.75">
       <c r="A64" s="3">
         <v>2</v>
       </c>
@@ -5000,8 +5204,11 @@
       <c r="V64" s="6"/>
       <c r="W64" s="6"/>
       <c r="X64" s="6"/>
-    </row>
-    <row r="65" spans="1:24" ht="15.75">
+      <c r="Y64" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" ht="15.75">
       <c r="A65" s="3">
         <v>2</v>
       </c>
@@ -5067,8 +5274,11 @@
       <c r="V65" s="6"/>
       <c r="W65" s="6"/>
       <c r="X65" s="6"/>
-    </row>
-    <row r="66" spans="1:24" ht="15.75">
+      <c r="Y65" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" ht="15.75">
       <c r="A66" s="3">
         <v>2</v>
       </c>
@@ -5134,8 +5344,11 @@
       <c r="V66" s="6"/>
       <c r="W66" s="6"/>
       <c r="X66" s="6"/>
-    </row>
-    <row r="67" spans="1:24" ht="15.75">
+      <c r="Y66" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" ht="15.75">
       <c r="A67" s="3">
         <v>2</v>
       </c>
@@ -5201,8 +5414,11 @@
       <c r="V67" s="6"/>
       <c r="W67" s="6"/>
       <c r="X67" s="6"/>
-    </row>
-    <row r="68" spans="1:24" ht="15.75">
+      <c r="Y67" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" ht="15.75">
       <c r="A68" s="3">
         <v>2</v>
       </c>
@@ -5268,8 +5484,11 @@
       <c r="V68" s="6"/>
       <c r="W68" s="6"/>
       <c r="X68" s="6"/>
-    </row>
-    <row r="69" spans="1:24" ht="15.75">
+      <c r="Y68" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" ht="15.75">
       <c r="A69" s="3">
         <v>2</v>
       </c>
@@ -5335,8 +5554,11 @@
       <c r="V69" s="6"/>
       <c r="W69" s="6"/>
       <c r="X69" s="6"/>
-    </row>
-    <row r="70" spans="1:24" ht="15.75">
+      <c r="Y69" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" ht="15.75">
       <c r="A70" s="3">
         <v>2</v>
       </c>
@@ -5402,8 +5624,11 @@
       <c r="V70" s="6"/>
       <c r="W70" s="6"/>
       <c r="X70" s="6"/>
-    </row>
-    <row r="71" spans="1:24" ht="15.75">
+      <c r="Y70" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" ht="15.75">
       <c r="A71" s="3">
         <v>2</v>
       </c>
@@ -5469,8 +5694,11 @@
       <c r="V71" s="6"/>
       <c r="W71" s="6"/>
       <c r="X71" s="6"/>
-    </row>
-    <row r="72" spans="1:24" ht="15.75">
+      <c r="Y71" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" ht="15.75">
       <c r="A72" s="3">
         <v>2</v>
       </c>
@@ -5536,8 +5764,11 @@
       <c r="V72" s="6"/>
       <c r="W72" s="6"/>
       <c r="X72" s="6"/>
-    </row>
-    <row r="73" spans="1:24" ht="15.75">
+      <c r="Y72" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" ht="15.75">
       <c r="A73" s="3">
         <v>2</v>
       </c>
@@ -5603,8 +5834,11 @@
       <c r="V73" s="6"/>
       <c r="W73" s="6"/>
       <c r="X73" s="6"/>
-    </row>
-    <row r="74" spans="1:24" ht="15.75">
+      <c r="Y73" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" ht="15.75">
       <c r="A74" s="3">
         <v>2</v>
       </c>
@@ -5670,8 +5904,11 @@
       <c r="V74" s="6"/>
       <c r="W74" s="6"/>
       <c r="X74" s="6"/>
-    </row>
-    <row r="75" spans="1:24" ht="15.75">
+      <c r="Y74" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" ht="15.75">
       <c r="A75" s="3">
         <v>2</v>
       </c>
@@ -5737,8 +5974,11 @@
       <c r="V75" s="6"/>
       <c r="W75" s="6"/>
       <c r="X75" s="6"/>
-    </row>
-    <row r="76" spans="1:24" ht="15.75">
+      <c r="Y75" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" ht="15.75">
       <c r="A76" s="3">
         <v>2</v>
       </c>
@@ -5804,8 +6044,11 @@
       <c r="V76" s="6"/>
       <c r="W76" s="6"/>
       <c r="X76" s="6"/>
-    </row>
-    <row r="77" spans="1:24" ht="15.75">
+      <c r="Y76" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" ht="15.75">
       <c r="A77" s="3">
         <v>2</v>
       </c>
@@ -5871,8 +6114,11 @@
       <c r="V77" s="6"/>
       <c r="W77" s="6"/>
       <c r="X77" s="6"/>
-    </row>
-    <row r="78" spans="1:24" ht="15.75">
+      <c r="Y77" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" ht="15.75">
       <c r="A78" s="3">
         <v>2</v>
       </c>
@@ -5938,8 +6184,11 @@
       <c r="V78" s="6"/>
       <c r="W78" s="6"/>
       <c r="X78" s="6"/>
-    </row>
-    <row r="79" spans="1:24" ht="15.75">
+      <c r="Y78" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" ht="15.75">
       <c r="A79" s="3">
         <v>2</v>
       </c>
@@ -6005,8 +6254,11 @@
       <c r="V79" s="6"/>
       <c r="W79" s="6"/>
       <c r="X79" s="6"/>
-    </row>
-    <row r="80" spans="1:24" ht="15.75">
+      <c r="Y79" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" ht="15.75">
       <c r="A80" s="3">
         <v>2</v>
       </c>
@@ -6078,8 +6330,11 @@
       <c r="X80" s="6">
         <v>0.59489999999999998</v>
       </c>
-    </row>
-    <row r="81" spans="1:24" ht="15.75">
+      <c r="Y80" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" ht="15.75">
       <c r="A81" s="3">
         <v>2</v>
       </c>
@@ -6151,8 +6406,11 @@
       <c r="X81" s="6">
         <v>0.54491999999999996</v>
       </c>
-    </row>
-    <row r="82" spans="1:24" ht="15.75">
+      <c r="Y81" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" ht="15.75">
       <c r="A82" s="3">
         <v>2</v>
       </c>
@@ -6224,8 +6482,11 @@
       <c r="X82" s="6">
         <v>0.49985000000000002</v>
       </c>
-    </row>
-    <row r="83" spans="1:24" ht="15.75">
+      <c r="Y82" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" ht="15.75">
       <c r="A83" s="3">
         <v>2</v>
       </c>
@@ -6297,8 +6558,11 @@
       <c r="X83" s="6">
         <v>0.45944000000000002</v>
       </c>
-    </row>
-    <row r="84" spans="1:24" ht="15.75">
+      <c r="Y83" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" ht="15.75">
       <c r="A84" s="3">
         <v>2</v>
       </c>
@@ -6370,8 +6634,11 @@
       <c r="X84" s="6">
         <v>0.41963</v>
       </c>
-    </row>
-    <row r="85" spans="1:24" ht="15.75">
+      <c r="Y84" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" ht="15.75">
       <c r="A85" s="3">
         <v>2</v>
       </c>
@@ -6443,8 +6710,11 @@
       <c r="X85" s="6">
         <v>0.38558999999999999</v>
       </c>
-    </row>
-    <row r="86" spans="1:24" ht="15.75">
+      <c r="Y85" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" ht="15.75">
       <c r="A86" s="3">
         <v>2</v>
       </c>
@@ -6516,8 +6786,11 @@
       <c r="X86" s="6">
         <v>0.32377</v>
       </c>
-    </row>
-    <row r="87" spans="1:24" ht="15.75">
+      <c r="Y86" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" ht="15.75">
       <c r="A87" s="3">
         <v>2</v>
       </c>
@@ -6589,8 +6862,11 @@
       <c r="X87" s="6">
         <v>0.27279999999999999</v>
       </c>
-    </row>
-    <row r="88" spans="1:24" ht="15.75">
+      <c r="Y87" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" ht="15.75">
       <c r="A88" s="3">
         <v>2</v>
       </c>
@@ -6662,8 +6938,11 @@
       <c r="X88" s="6">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="89" spans="1:24" ht="15.75">
+      <c r="Y88" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" ht="15.75">
       <c r="A89" s="3">
         <v>2</v>
       </c>
@@ -6735,8 +7014,11 @@
       <c r="X89" s="6">
         <v>0.22911999999999999</v>
       </c>
-    </row>
-    <row r="90" spans="1:24" ht="15.75">
+      <c r="Y89" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" ht="15.75">
       <c r="A90" s="3">
         <v>2</v>
       </c>
@@ -6808,8 +7090,11 @@
       <c r="X90" s="6">
         <v>0.21004999999999999</v>
       </c>
-    </row>
-    <row r="91" spans="1:24" ht="15.75">
+      <c r="Y90" s="13">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" ht="15.75">
       <c r="A91" s="3">
         <v>3</v>
       </c>
@@ -6875,8 +7160,11 @@
       <c r="V91" s="6"/>
       <c r="W91" s="6"/>
       <c r="X91" s="6"/>
-    </row>
-    <row r="92" spans="1:24" ht="15.75">
+      <c r="Y91" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" ht="15.75">
       <c r="A92" s="3">
         <v>3</v>
       </c>
@@ -6942,8 +7230,11 @@
       <c r="V92" s="6"/>
       <c r="W92" s="6"/>
       <c r="X92" s="6"/>
-    </row>
-    <row r="93" spans="1:24" ht="15.75">
+      <c r="Y92" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" ht="15.75">
       <c r="A93" s="3">
         <v>3</v>
       </c>
@@ -7009,8 +7300,11 @@
       <c r="V93" s="6"/>
       <c r="W93" s="6"/>
       <c r="X93" s="6"/>
-    </row>
-    <row r="94" spans="1:24" ht="15.75">
+      <c r="Y93" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" ht="15.75">
       <c r="A94" s="3">
         <v>3</v>
       </c>
@@ -7076,8 +7370,11 @@
       <c r="V94" s="6"/>
       <c r="W94" s="6"/>
       <c r="X94" s="6"/>
-    </row>
-    <row r="95" spans="1:24" ht="15.75">
+      <c r="Y94" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" ht="15.75">
       <c r="A95" s="3">
         <v>3</v>
       </c>
@@ -7143,8 +7440,11 @@
       <c r="V95" s="6"/>
       <c r="W95" s="6"/>
       <c r="X95" s="6"/>
-    </row>
-    <row r="96" spans="1:24" ht="15.75">
+      <c r="Y95" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" ht="15.75">
       <c r="A96" s="3">
         <v>3</v>
       </c>
@@ -7210,8 +7510,11 @@
       <c r="V96" s="6"/>
       <c r="W96" s="6"/>
       <c r="X96" s="6"/>
-    </row>
-    <row r="97" spans="1:24" ht="15.75">
+      <c r="Y96" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" ht="15.75">
       <c r="A97" s="3">
         <v>3</v>
       </c>
@@ -7277,8 +7580,11 @@
       <c r="V97" s="6"/>
       <c r="W97" s="6"/>
       <c r="X97" s="6"/>
-    </row>
-    <row r="98" spans="1:24" ht="15.75">
+      <c r="Y97" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" ht="15.75">
       <c r="A98" s="3">
         <v>3</v>
       </c>
@@ -7344,8 +7650,11 @@
       <c r="V98" s="6"/>
       <c r="W98" s="6"/>
       <c r="X98" s="6"/>
-    </row>
-    <row r="99" spans="1:24" ht="15.75">
+      <c r="Y98" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" ht="15.75">
       <c r="A99" s="3">
         <v>3</v>
       </c>
@@ -7411,8 +7720,11 @@
       <c r="V99" s="6"/>
       <c r="W99" s="6"/>
       <c r="X99" s="6"/>
-    </row>
-    <row r="100" spans="1:24" ht="15.75">
+      <c r="Y99" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" ht="15.75">
       <c r="A100" s="3">
         <v>3</v>
       </c>
@@ -7478,8 +7790,11 @@
       <c r="V100" s="6"/>
       <c r="W100" s="6"/>
       <c r="X100" s="6"/>
-    </row>
-    <row r="101" spans="1:24" ht="15.75">
+      <c r="Y100" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" ht="15.75">
       <c r="A101" s="3">
         <v>3</v>
       </c>
@@ -7545,8 +7860,11 @@
       <c r="V101" s="6"/>
       <c r="W101" s="6"/>
       <c r="X101" s="6"/>
-    </row>
-    <row r="102" spans="1:24" ht="15.75">
+      <c r="Y101" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" ht="15.75">
       <c r="A102" s="3">
         <v>3</v>
       </c>
@@ -7612,8 +7930,11 @@
       <c r="V102" s="6"/>
       <c r="W102" s="6"/>
       <c r="X102" s="6"/>
-    </row>
-    <row r="103" spans="1:24" ht="15.75">
+      <c r="Y102" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" ht="15.75">
       <c r="A103" s="3">
         <v>3</v>
       </c>
@@ -7679,8 +8000,11 @@
       <c r="V103" s="6"/>
       <c r="W103" s="6"/>
       <c r="X103" s="6"/>
-    </row>
-    <row r="104" spans="1:24" ht="15.75">
+      <c r="Y103" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" ht="15.75">
       <c r="A104" s="3">
         <v>3</v>
       </c>
@@ -7746,8 +8070,11 @@
       <c r="V104" s="6"/>
       <c r="W104" s="6"/>
       <c r="X104" s="6"/>
-    </row>
-    <row r="105" spans="1:24" ht="15.75">
+      <c r="Y104" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" ht="15.75">
       <c r="A105" s="3">
         <v>3</v>
       </c>
@@ -7813,8 +8140,11 @@
       <c r="V105" s="6"/>
       <c r="W105" s="6"/>
       <c r="X105" s="6"/>
-    </row>
-    <row r="106" spans="1:24" ht="15.75">
+      <c r="Y105" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" ht="15.75">
       <c r="A106" s="3">
         <v>3</v>
       </c>
@@ -7880,8 +8210,11 @@
       <c r="V106" s="6"/>
       <c r="W106" s="6"/>
       <c r="X106" s="6"/>
-    </row>
-    <row r="107" spans="1:24" ht="15.75">
+      <c r="Y106" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" ht="15.75">
       <c r="A107" s="3">
         <v>3</v>
       </c>
@@ -7947,8 +8280,11 @@
       <c r="V107" s="6"/>
       <c r="W107" s="6"/>
       <c r="X107" s="6"/>
-    </row>
-    <row r="108" spans="1:24" ht="15.75">
+      <c r="Y107" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" ht="15.75">
       <c r="A108" s="3">
         <v>3</v>
       </c>
@@ -8014,8 +8350,11 @@
       <c r="V108" s="6"/>
       <c r="W108" s="6"/>
       <c r="X108" s="6"/>
-    </row>
-    <row r="109" spans="1:24" ht="15.75">
+      <c r="Y108" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" ht="15.75">
       <c r="A109" s="3">
         <v>3</v>
       </c>
@@ -8081,8 +8420,11 @@
       <c r="V109" s="6"/>
       <c r="W109" s="6"/>
       <c r="X109" s="6"/>
-    </row>
-    <row r="110" spans="1:24" ht="15.75">
+      <c r="Y109" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" ht="15.75">
       <c r="A110" s="3">
         <v>3</v>
       </c>
@@ -8148,8 +8490,11 @@
       <c r="V110" s="6"/>
       <c r="W110" s="6"/>
       <c r="X110" s="6"/>
-    </row>
-    <row r="111" spans="1:24" ht="15.75">
+      <c r="Y110" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" ht="15.75">
       <c r="A111" s="3">
         <v>3</v>
       </c>
@@ -8215,8 +8560,11 @@
       <c r="V111" s="6"/>
       <c r="W111" s="6"/>
       <c r="X111" s="6"/>
-    </row>
-    <row r="112" spans="1:24" ht="15.75">
+      <c r="Y111" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" ht="15.75">
       <c r="A112" s="3">
         <v>3</v>
       </c>
@@ -8282,8 +8630,11 @@
       <c r="V112" s="6"/>
       <c r="W112" s="6"/>
       <c r="X112" s="6"/>
-    </row>
-    <row r="113" spans="1:24" ht="15.75">
+      <c r="Y112" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" ht="15.75">
       <c r="A113" s="3">
         <v>3</v>
       </c>
@@ -8349,8 +8700,11 @@
       <c r="V113" s="6"/>
       <c r="W113" s="6"/>
       <c r="X113" s="6"/>
-    </row>
-    <row r="114" spans="1:24" ht="15.75">
+      <c r="Y113" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" ht="15.75">
       <c r="A114" s="3">
         <v>3</v>
       </c>
@@ -8416,8 +8770,11 @@
       <c r="V114" s="6"/>
       <c r="W114" s="6"/>
       <c r="X114" s="6"/>
-    </row>
-    <row r="115" spans="1:24" ht="15.75">
+      <c r="Y114" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" ht="15.75">
       <c r="A115" s="3">
         <v>3</v>
       </c>
@@ -8483,8 +8840,11 @@
       <c r="V115" s="6"/>
       <c r="W115" s="6"/>
       <c r="X115" s="6"/>
-    </row>
-    <row r="116" spans="1:24" ht="15.75">
+      <c r="Y115" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" ht="15.75">
       <c r="A116" s="3">
         <v>3</v>
       </c>
@@ -8550,8 +8910,11 @@
       <c r="V116" s="6"/>
       <c r="W116" s="6"/>
       <c r="X116" s="6"/>
-    </row>
-    <row r="117" spans="1:24" ht="15.75">
+      <c r="Y116" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" ht="15.75">
       <c r="A117" s="3">
         <v>3</v>
       </c>
@@ -8617,8 +8980,11 @@
       <c r="V117" s="6"/>
       <c r="W117" s="6"/>
       <c r="X117" s="6"/>
-    </row>
-    <row r="118" spans="1:24" ht="15.75">
+      <c r="Y117" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" ht="15.75">
       <c r="A118" s="3">
         <v>3</v>
       </c>
@@ -8684,8 +9050,11 @@
       <c r="V118" s="6"/>
       <c r="W118" s="6"/>
       <c r="X118" s="6"/>
-    </row>
-    <row r="119" spans="1:24" ht="15.75">
+      <c r="Y118" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" ht="15.75">
       <c r="A119" s="3">
         <v>3</v>
       </c>
@@ -8751,8 +9120,11 @@
       <c r="V119" s="6"/>
       <c r="W119" s="6"/>
       <c r="X119" s="6"/>
-    </row>
-    <row r="120" spans="1:24" ht="15.75">
+      <c r="Y119" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" ht="15.75">
       <c r="A120" s="3">
         <v>3</v>
       </c>
@@ -8818,8 +9190,11 @@
       <c r="V120" s="6"/>
       <c r="W120" s="6"/>
       <c r="X120" s="6"/>
-    </row>
-    <row r="121" spans="1:24" ht="15.75">
+      <c r="Y120" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" ht="15.75">
       <c r="A121" s="3">
         <v>3</v>
       </c>
@@ -8885,8 +9260,11 @@
       <c r="V121" s="6"/>
       <c r="W121" s="6"/>
       <c r="X121" s="6"/>
-    </row>
-    <row r="122" spans="1:24" ht="15.75">
+      <c r="Y121" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" ht="15.75">
       <c r="A122" s="3">
         <v>3</v>
       </c>
@@ -8952,8 +9330,11 @@
       <c r="V122" s="6"/>
       <c r="W122" s="6"/>
       <c r="X122" s="6"/>
-    </row>
-    <row r="123" spans="1:24" ht="15.75">
+      <c r="Y122" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" ht="15.75">
       <c r="A123" s="3">
         <v>3</v>
       </c>
@@ -9019,8 +9400,11 @@
       <c r="V123" s="6"/>
       <c r="W123" s="6"/>
       <c r="X123" s="6"/>
-    </row>
-    <row r="124" spans="1:24" ht="15.75">
+      <c r="Y123" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" ht="15.75">
       <c r="A124" s="3">
         <v>3</v>
       </c>
@@ -9086,8 +9470,11 @@
       <c r="V124" s="6"/>
       <c r="W124" s="6"/>
       <c r="X124" s="6"/>
-    </row>
-    <row r="125" spans="1:24" ht="15.75">
+      <c r="Y124" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" ht="15.75">
       <c r="A125" s="3">
         <v>3</v>
       </c>
@@ -9153,8 +9540,11 @@
       <c r="V125" s="6"/>
       <c r="W125" s="6"/>
       <c r="X125" s="6"/>
-    </row>
-    <row r="126" spans="1:24" ht="15.75">
+      <c r="Y125" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" ht="15.75">
       <c r="A126" s="3">
         <v>3</v>
       </c>
@@ -9220,8 +9610,11 @@
       <c r="V126" s="6"/>
       <c r="W126" s="6"/>
       <c r="X126" s="6"/>
-    </row>
-    <row r="127" spans="1:24" ht="15.75">
+      <c r="Y126" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" ht="15.75">
       <c r="A127" s="3">
         <v>3</v>
       </c>
@@ -9287,8 +9680,11 @@
       <c r="V127" s="6"/>
       <c r="W127" s="6"/>
       <c r="X127" s="6"/>
-    </row>
-    <row r="128" spans="1:24" ht="15.75">
+      <c r="Y127" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" ht="15.75">
       <c r="A128" s="3">
         <v>3</v>
       </c>
@@ -9354,8 +9750,11 @@
       <c r="V128" s="6"/>
       <c r="W128" s="6"/>
       <c r="X128" s="6"/>
-    </row>
-    <row r="129" spans="1:24" ht="15.75">
+      <c r="Y128" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" ht="15.75">
       <c r="A129" s="3">
         <v>3</v>
       </c>
@@ -9421,8 +9820,11 @@
       <c r="V129" s="6"/>
       <c r="W129" s="6"/>
       <c r="X129" s="6"/>
-    </row>
-    <row r="130" spans="1:24" ht="15.75">
+      <c r="Y129" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" ht="15.75">
       <c r="A130" s="3">
         <v>3</v>
       </c>
@@ -9488,8 +9890,11 @@
       <c r="V130" s="6"/>
       <c r="W130" s="6"/>
       <c r="X130" s="6"/>
-    </row>
-    <row r="131" spans="1:24" ht="15.75">
+      <c r="Y130" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" ht="15.75">
       <c r="A131" s="3">
         <v>3</v>
       </c>
@@ -9555,8 +9960,11 @@
       <c r="V131" s="6"/>
       <c r="W131" s="6"/>
       <c r="X131" s="6"/>
-    </row>
-    <row r="132" spans="1:24" ht="15.75">
+      <c r="Y131" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" ht="15.75">
       <c r="A132" s="3">
         <v>3</v>
       </c>
@@ -9622,8 +10030,11 @@
       <c r="V132" s="6"/>
       <c r="W132" s="6"/>
       <c r="X132" s="6"/>
-    </row>
-    <row r="133" spans="1:24" ht="15.75">
+      <c r="Y132" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" ht="15.75">
       <c r="A133" s="3">
         <v>3</v>
       </c>
@@ -9689,8 +10100,11 @@
       <c r="V133" s="6"/>
       <c r="W133" s="6"/>
       <c r="X133" s="6"/>
-    </row>
-    <row r="134" spans="1:24" ht="15.75">
+      <c r="Y133" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" ht="15.75">
       <c r="A134" s="3">
         <v>3</v>
       </c>
@@ -9756,8 +10170,11 @@
       <c r="V134" s="6"/>
       <c r="W134" s="6"/>
       <c r="X134" s="6"/>
-    </row>
-    <row r="135" spans="1:24" ht="15.75">
+      <c r="Y134" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" ht="15.75">
       <c r="A135" s="3">
         <v>3</v>
       </c>
@@ -9823,8 +10240,11 @@
       <c r="V135" s="6"/>
       <c r="W135" s="6"/>
       <c r="X135" s="6"/>
-    </row>
-    <row r="136" spans="1:24" ht="15.75">
+      <c r="Y135" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" ht="15.75">
       <c r="A136" s="3">
         <v>3</v>
       </c>
@@ -9890,8 +10310,11 @@
       <c r="V136" s="6"/>
       <c r="W136" s="6"/>
       <c r="X136" s="6"/>
-    </row>
-    <row r="137" spans="1:24" ht="15.75">
+      <c r="Y136" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" ht="15.75">
       <c r="A137" s="3">
         <v>3</v>
       </c>
@@ -9957,8 +10380,11 @@
       <c r="V137" s="6"/>
       <c r="W137" s="6"/>
       <c r="X137" s="6"/>
-    </row>
-    <row r="138" spans="1:24" ht="15.75">
+      <c r="Y137" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" ht="15.75">
       <c r="A138" s="3">
         <v>3</v>
       </c>
@@ -10030,8 +10456,11 @@
       <c r="X138" s="6">
         <v>0.70296000000000003</v>
       </c>
-    </row>
-    <row r="139" spans="1:24" ht="15.75">
+      <c r="Y138" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" ht="15.75">
       <c r="A139" s="3">
         <v>3</v>
       </c>
@@ -10103,8 +10532,11 @@
       <c r="X139" s="6">
         <v>0.59460999999999997</v>
       </c>
-    </row>
-    <row r="140" spans="1:24" ht="15.75">
+      <c r="Y139" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" ht="15.75">
       <c r="A140" s="3">
         <v>3</v>
       </c>
@@ -10176,8 +10608,11 @@
       <c r="X140" s="6">
         <v>0.49615999999999999</v>
       </c>
-    </row>
-    <row r="141" spans="1:24" ht="15.75">
+      <c r="Y140" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" ht="15.75">
       <c r="A141" s="3">
         <v>3</v>
       </c>
@@ -10249,8 +10684,11 @@
       <c r="X141" s="6">
         <v>0.41694999999999999</v>
       </c>
-    </row>
-    <row r="142" spans="1:24" ht="15.75">
+      <c r="Y141" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" ht="15.75">
       <c r="A142" s="3">
         <v>3</v>
       </c>
@@ -10322,8 +10760,11 @@
       <c r="X142" s="6">
         <v>0.41904999999999998</v>
       </c>
-    </row>
-    <row r="143" spans="1:24" ht="15.75">
+      <c r="Y142" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" ht="15.75">
       <c r="A143" s="3">
         <v>3</v>
       </c>
@@ -10395,8 +10836,11 @@
       <c r="X143" s="6">
         <v>0.35309000000000001</v>
       </c>
-    </row>
-    <row r="144" spans="1:24" ht="15.75">
+      <c r="Y143" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" ht="15.75">
       <c r="A144" s="3">
         <v>3</v>
       </c>
@@ -10468,8 +10912,11 @@
       <c r="X144" s="6">
         <v>0.29635</v>
       </c>
-    </row>
-    <row r="145" spans="1:24" ht="15.75">
+      <c r="Y144" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" ht="15.75">
       <c r="A145" s="3">
         <v>3</v>
       </c>
@@ -10541,8 +10988,11 @@
       <c r="X145" s="6">
         <v>0.24943000000000001</v>
       </c>
-    </row>
-    <row r="146" spans="1:24" ht="15.75">
+      <c r="Y145" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" ht="15.75">
       <c r="A146" s="3">
         <v>3</v>
       </c>
@@ -10614,8 +11064,11 @@
       <c r="X146" s="6">
         <v>0.21024000000000001</v>
       </c>
-    </row>
-    <row r="147" spans="1:24" ht="15.75">
+      <c r="Y146" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" ht="15.75">
       <c r="A147" s="3">
         <v>3</v>
       </c>
@@ -10687,8 +11140,11 @@
       <c r="X147" s="6">
         <v>0.17638000000000001</v>
       </c>
-    </row>
-    <row r="148" spans="1:24" ht="15.75">
+      <c r="Y147" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" ht="15.75">
       <c r="A148" s="3">
         <v>3</v>
       </c>
@@ -10760,8 +11216,11 @@
       <c r="X148" s="6">
         <v>0.14902000000000001</v>
       </c>
-    </row>
-    <row r="149" spans="1:24" ht="15.75">
+      <c r="Y148" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" ht="15.75">
       <c r="A149" s="3">
         <v>4</v>
       </c>
@@ -10827,8 +11286,11 @@
       <c r="V149" s="6"/>
       <c r="W149" s="6"/>
       <c r="X149" s="6"/>
-    </row>
-    <row r="150" spans="1:24" ht="15.75">
+      <c r="Y149" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" ht="15.75">
       <c r="A150" s="3">
         <v>4</v>
       </c>
@@ -10894,8 +11356,11 @@
       <c r="V150" s="6"/>
       <c r="W150" s="6"/>
       <c r="X150" s="6"/>
-    </row>
-    <row r="151" spans="1:24" ht="15.75">
+      <c r="Y150" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" ht="15.75">
       <c r="A151" s="3">
         <v>4</v>
       </c>
@@ -10961,8 +11426,11 @@
       <c r="V151" s="6"/>
       <c r="W151" s="6"/>
       <c r="X151" s="6"/>
-    </row>
-    <row r="152" spans="1:24" ht="15.75">
+      <c r="Y151" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" ht="15.75">
       <c r="A152" s="3">
         <v>4</v>
       </c>
@@ -11028,8 +11496,11 @@
       <c r="V152" s="6"/>
       <c r="W152" s="6"/>
       <c r="X152" s="6"/>
-    </row>
-    <row r="153" spans="1:24" ht="15.75">
+      <c r="Y152" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" ht="15.75">
       <c r="A153" s="3">
         <v>4</v>
       </c>
@@ -11095,8 +11566,11 @@
       <c r="V153" s="6"/>
       <c r="W153" s="6"/>
       <c r="X153" s="6"/>
-    </row>
-    <row r="154" spans="1:24" ht="15.75">
+      <c r="Y153" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" ht="15.75">
       <c r="A154" s="3">
         <v>4</v>
       </c>
@@ -11162,8 +11636,11 @@
       <c r="V154" s="6"/>
       <c r="W154" s="6"/>
       <c r="X154" s="6"/>
-    </row>
-    <row r="155" spans="1:24" ht="15.75">
+      <c r="Y154" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" ht="15.75">
       <c r="A155" s="3">
         <v>4</v>
       </c>
@@ -11229,8 +11706,11 @@
       <c r="V155" s="6"/>
       <c r="W155" s="6"/>
       <c r="X155" s="6"/>
-    </row>
-    <row r="156" spans="1:24" ht="15.75">
+      <c r="Y155" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" ht="15.75">
       <c r="A156" s="3">
         <v>4</v>
       </c>
@@ -11296,8 +11776,11 @@
       <c r="V156" s="6"/>
       <c r="W156" s="6"/>
       <c r="X156" s="6"/>
-    </row>
-    <row r="157" spans="1:24" ht="15.75">
+      <c r="Y156" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" ht="15.75">
       <c r="A157" s="3">
         <v>4</v>
       </c>
@@ -11363,8 +11846,11 @@
       <c r="V157" s="6"/>
       <c r="W157" s="6"/>
       <c r="X157" s="6"/>
-    </row>
-    <row r="158" spans="1:24" ht="15.75">
+      <c r="Y157" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" ht="15.75">
       <c r="A158" s="3">
         <v>4</v>
       </c>
@@ -11430,8 +11916,11 @@
       <c r="V158" s="6"/>
       <c r="W158" s="6"/>
       <c r="X158" s="6"/>
-    </row>
-    <row r="159" spans="1:24" ht="15.75">
+      <c r="Y158" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" ht="15.75">
       <c r="A159" s="3">
         <v>4</v>
       </c>
@@ -11497,8 +11986,11 @@
       <c r="V159" s="6"/>
       <c r="W159" s="6"/>
       <c r="X159" s="6"/>
-    </row>
-    <row r="160" spans="1:24" ht="15.75">
+      <c r="Y159" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" ht="15.75">
       <c r="A160" s="3">
         <v>4</v>
       </c>
@@ -11564,8 +12056,11 @@
       <c r="V160" s="6"/>
       <c r="W160" s="6"/>
       <c r="X160" s="6"/>
-    </row>
-    <row r="161" spans="1:24" ht="15.75">
+      <c r="Y160" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="161" spans="1:25" ht="15.75">
       <c r="A161" s="3">
         <v>4</v>
       </c>
@@ -11631,8 +12126,11 @@
       <c r="V161" s="6"/>
       <c r="W161" s="6"/>
       <c r="X161" s="6"/>
-    </row>
-    <row r="162" spans="1:24" ht="15.75">
+      <c r="Y161" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25" ht="15.75">
       <c r="A162" s="3">
         <v>4</v>
       </c>
@@ -11698,8 +12196,11 @@
       <c r="V162" s="6"/>
       <c r="W162" s="6"/>
       <c r="X162" s="6"/>
-    </row>
-    <row r="163" spans="1:24" ht="15.75">
+      <c r="Y162" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25" ht="15.75">
       <c r="A163" s="3">
         <v>4</v>
       </c>
@@ -11765,8 +12266,11 @@
       <c r="V163" s="6"/>
       <c r="W163" s="6"/>
       <c r="X163" s="6"/>
-    </row>
-    <row r="164" spans="1:24" ht="15.75">
+      <c r="Y163" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25" ht="15.75">
       <c r="A164" s="3">
         <v>4</v>
       </c>
@@ -11832,8 +12336,11 @@
       <c r="V164" s="6"/>
       <c r="W164" s="6"/>
       <c r="X164" s="6"/>
-    </row>
-    <row r="165" spans="1:24" ht="15.75">
+      <c r="Y164" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="165" spans="1:25" ht="15.75">
       <c r="A165" s="3">
         <v>4</v>
       </c>
@@ -11899,8 +12406,11 @@
       <c r="V165" s="6"/>
       <c r="W165" s="6"/>
       <c r="X165" s="6"/>
-    </row>
-    <row r="166" spans="1:24" ht="15.75">
+      <c r="Y165" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="166" spans="1:25" ht="15.75">
       <c r="A166" s="3">
         <v>4</v>
       </c>
@@ -11966,8 +12476,11 @@
       <c r="V166" s="6"/>
       <c r="W166" s="6"/>
       <c r="X166" s="6"/>
-    </row>
-    <row r="167" spans="1:24" ht="15.75">
+      <c r="Y166" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25" ht="15.75">
       <c r="A167" s="3">
         <v>4</v>
       </c>
@@ -12033,8 +12546,11 @@
       <c r="V167" s="6"/>
       <c r="W167" s="6"/>
       <c r="X167" s="6"/>
-    </row>
-    <row r="168" spans="1:24" ht="15.75">
+      <c r="Y167" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="168" spans="1:25" ht="15.75">
       <c r="A168" s="3">
         <v>4</v>
       </c>
@@ -12100,8 +12616,11 @@
       <c r="V168" s="6"/>
       <c r="W168" s="6"/>
       <c r="X168" s="6"/>
-    </row>
-    <row r="169" spans="1:24" ht="15.75">
+      <c r="Y168" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="169" spans="1:25" ht="15.75">
       <c r="A169" s="3">
         <v>4</v>
       </c>
@@ -12167,8 +12686,11 @@
       <c r="V169" s="6"/>
       <c r="W169" s="6"/>
       <c r="X169" s="6"/>
-    </row>
-    <row r="170" spans="1:24" ht="15.75">
+      <c r="Y169" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25" ht="15.75">
       <c r="A170" s="3">
         <v>4</v>
       </c>
@@ -12240,8 +12762,11 @@
       <c r="X170" s="6">
         <v>1.0062</v>
       </c>
-    </row>
-    <row r="171" spans="1:24" ht="15.75">
+      <c r="Y170" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="171" spans="1:25" ht="15.75">
       <c r="A171" s="3">
         <v>4</v>
       </c>
@@ -12313,8 +12838,11 @@
       <c r="X171" s="6">
         <v>0.80091000000000001</v>
       </c>
-    </row>
-    <row r="172" spans="1:24" ht="15.75">
+      <c r="Y171" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="172" spans="1:25" ht="15.75">
       <c r="A172" s="3">
         <v>4</v>
       </c>
@@ -12386,8 +12914,11 @@
       <c r="X172" s="6">
         <v>0.69994000000000001</v>
       </c>
-    </row>
-    <row r="173" spans="1:24" ht="15.75">
+      <c r="Y172" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="173" spans="1:25" ht="15.75">
       <c r="A173" s="3">
         <v>4</v>
       </c>
@@ -12459,8 +12990,11 @@
       <c r="X173" s="6">
         <v>0.59855999999999998</v>
       </c>
-    </row>
-    <row r="174" spans="1:24" ht="15.75">
+      <c r="Y173" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="174" spans="1:25" ht="15.75">
       <c r="A174" s="3">
         <v>4</v>
       </c>
@@ -12532,8 +13066,11 @@
       <c r="X174" s="6">
         <v>0.45794000000000001</v>
       </c>
-    </row>
-    <row r="175" spans="1:24" ht="15.75">
+      <c r="Y174" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="175" spans="1:25" ht="15.75">
       <c r="A175" s="3">
         <v>4</v>
       </c>
@@ -12605,8 +13142,11 @@
       <c r="X175" s="6">
         <v>0.59811000000000003</v>
       </c>
-    </row>
-    <row r="176" spans="1:24" ht="15.75">
+      <c r="Y175" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="176" spans="1:25" ht="15.75">
       <c r="A176" s="3">
         <v>4</v>
       </c>
@@ -12678,8 +13218,11 @@
       <c r="X176" s="6">
         <v>0.70711000000000002</v>
       </c>
-    </row>
-    <row r="177" spans="1:24" ht="15.75">
+      <c r="Y176" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="177" spans="1:25" ht="15.75">
       <c r="A177" s="3">
         <v>4</v>
       </c>
@@ -12751,8 +13294,11 @@
       <c r="X177" s="6">
         <v>0.49830999999999998</v>
       </c>
-    </row>
-    <row r="178" spans="1:24" ht="15.75">
+      <c r="Y177" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="178" spans="1:25" ht="15.75">
       <c r="A178" s="3">
         <v>4</v>
       </c>
@@ -12824,8 +13370,11 @@
       <c r="X178" s="6">
         <v>0.40022999999999997</v>
       </c>
-    </row>
-    <row r="179" spans="1:24" ht="15.75">
+      <c r="Y178" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="179" spans="1:25" ht="15.75">
       <c r="A179" s="3">
         <v>4</v>
       </c>
@@ -12897,8 +13446,11 @@
       <c r="X179" s="6">
         <v>0.29975000000000002</v>
       </c>
-    </row>
-    <row r="180" spans="1:24" ht="15.75">
+      <c r="Y179" s="13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="180" spans="1:25" ht="15.75">
       <c r="A180" s="3">
         <v>5</v>
       </c>
@@ -12964,8 +13516,11 @@
       <c r="V180" s="6"/>
       <c r="W180" s="6"/>
       <c r="X180" s="6"/>
-    </row>
-    <row r="181" spans="1:24" ht="15.75">
+      <c r="Y180" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="181" spans="1:25" ht="15.75">
       <c r="A181" s="3">
         <v>5</v>
       </c>
@@ -13031,8 +13586,11 @@
       <c r="V181" s="6"/>
       <c r="W181" s="6"/>
       <c r="X181" s="6"/>
-    </row>
-    <row r="182" spans="1:24" ht="15.75">
+      <c r="Y181" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="182" spans="1:25" ht="15.75">
       <c r="A182" s="3">
         <v>5</v>
       </c>
@@ -13098,8 +13656,11 @@
       <c r="V182" s="6"/>
       <c r="W182" s="6"/>
       <c r="X182" s="6"/>
-    </row>
-    <row r="183" spans="1:24" ht="15.75">
+      <c r="Y182" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="183" spans="1:25" ht="15.75">
       <c r="A183" s="3">
         <v>5</v>
       </c>
@@ -13165,8 +13726,11 @@
       <c r="V183" s="6"/>
       <c r="W183" s="6"/>
       <c r="X183" s="6"/>
-    </row>
-    <row r="184" spans="1:24" ht="15.75">
+      <c r="Y183" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="184" spans="1:25" ht="15.75">
       <c r="A184" s="3">
         <v>5</v>
       </c>
@@ -13232,8 +13796,11 @@
       <c r="V184" s="6"/>
       <c r="W184" s="6"/>
       <c r="X184" s="6"/>
-    </row>
-    <row r="185" spans="1:24" ht="15.75">
+      <c r="Y184" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="185" spans="1:25" ht="15.75">
       <c r="A185" s="3">
         <v>5</v>
       </c>
@@ -13299,8 +13866,11 @@
       <c r="V185" s="6"/>
       <c r="W185" s="6"/>
       <c r="X185" s="6"/>
-    </row>
-    <row r="186" spans="1:24" ht="15.75">
+      <c r="Y185" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="186" spans="1:25" ht="15.75">
       <c r="A186" s="3">
         <v>5</v>
       </c>
@@ -13366,8 +13936,11 @@
       <c r="V186" s="6"/>
       <c r="W186" s="6"/>
       <c r="X186" s="6"/>
-    </row>
-    <row r="187" spans="1:24" ht="15.75">
+      <c r="Y186" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="187" spans="1:25" ht="15.75">
       <c r="A187" s="3">
         <v>5</v>
       </c>
@@ -13433,8 +14006,11 @@
       <c r="V187" s="6"/>
       <c r="W187" s="6"/>
       <c r="X187" s="6"/>
-    </row>
-    <row r="188" spans="1:24" ht="15.75">
+      <c r="Y187" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="188" spans="1:25" ht="15.75">
       <c r="A188" s="3">
         <v>5</v>
       </c>
@@ -13500,8 +14076,11 @@
       <c r="V188" s="6"/>
       <c r="W188" s="6"/>
       <c r="X188" s="6"/>
-    </row>
-    <row r="189" spans="1:24" ht="15.75">
+      <c r="Y188" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="189" spans="1:25" ht="15.75">
       <c r="A189" s="3">
         <v>5</v>
       </c>
@@ -13567,8 +14146,11 @@
       <c r="V189" s="6"/>
       <c r="W189" s="6"/>
       <c r="X189" s="6"/>
-    </row>
-    <row r="190" spans="1:24" ht="15.75">
+      <c r="Y189" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="190" spans="1:25" ht="15.75">
       <c r="A190" s="3">
         <v>5</v>
       </c>
@@ -13634,8 +14216,11 @@
       <c r="V190" s="6"/>
       <c r="W190" s="6"/>
       <c r="X190" s="6"/>
-    </row>
-    <row r="191" spans="1:24" ht="15.75">
+      <c r="Y190" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="191" spans="1:25" ht="15.75">
       <c r="A191" s="3">
         <v>5</v>
       </c>
@@ -13701,8 +14286,11 @@
       <c r="V191" s="6"/>
       <c r="W191" s="6"/>
       <c r="X191" s="6"/>
-    </row>
-    <row r="192" spans="1:24" ht="15.75">
+      <c r="Y191" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="192" spans="1:25" ht="15.75">
       <c r="A192" s="3">
         <v>5</v>
       </c>
@@ -13768,8 +14356,11 @@
       <c r="V192" s="6"/>
       <c r="W192" s="6"/>
       <c r="X192" s="6"/>
-    </row>
-    <row r="193" spans="1:24" ht="15.75">
+      <c r="Y192" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="193" spans="1:25" ht="15.75">
       <c r="A193" s="3">
         <v>5</v>
       </c>
@@ -13835,8 +14426,11 @@
       <c r="V193" s="6"/>
       <c r="W193" s="6"/>
       <c r="X193" s="6"/>
-    </row>
-    <row r="194" spans="1:24" ht="15.75">
+      <c r="Y193" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="194" spans="1:25" ht="15.75">
       <c r="A194" s="3">
         <v>5</v>
       </c>
@@ -13902,8 +14496,11 @@
       <c r="V194" s="6"/>
       <c r="W194" s="6"/>
       <c r="X194" s="6"/>
-    </row>
-    <row r="195" spans="1:24" ht="15.75">
+      <c r="Y194" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="195" spans="1:25" ht="15.75">
       <c r="A195" s="3">
         <v>5</v>
       </c>
@@ -13969,8 +14566,11 @@
       <c r="V195" s="6"/>
       <c r="W195" s="6"/>
       <c r="X195" s="6"/>
-    </row>
-    <row r="196" spans="1:24" ht="15.75">
+      <c r="Y195" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="196" spans="1:25" ht="15.75">
       <c r="A196" s="3">
         <v>5</v>
       </c>
@@ -14036,8 +14636,11 @@
       <c r="V196" s="6"/>
       <c r="W196" s="6"/>
       <c r="X196" s="6"/>
-    </row>
-    <row r="197" spans="1:24" ht="15.75">
+      <c r="Y196" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="197" spans="1:25" ht="15.75">
       <c r="A197" s="3">
         <v>5</v>
       </c>
@@ -14107,8 +14710,11 @@
       <c r="X197" s="6">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="198" spans="1:24" ht="15.75">
+      <c r="Y197" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="198" spans="1:25" ht="15.75">
       <c r="A198" s="3">
         <v>5</v>
       </c>
@@ -14178,8 +14784,11 @@
       <c r="X198" s="6">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="199" spans="1:24" ht="15.75">
+      <c r="Y198" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="199" spans="1:25" ht="15.75">
       <c r="A199" s="3">
         <v>5</v>
       </c>
@@ -14249,8 +14858,11 @@
       <c r="X199" s="6">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="200" spans="1:24" ht="15.75">
+      <c r="Y199" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="200" spans="1:25" ht="15.75">
       <c r="A200" s="3">
         <v>5</v>
       </c>
@@ -14320,8 +14932,11 @@
       <c r="X200" s="6">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="201" spans="1:24" ht="15.75">
+      <c r="Y200" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="201" spans="1:25" ht="15.75">
       <c r="A201" s="3">
         <v>5</v>
       </c>
@@ -14391,8 +15006,11 @@
       <c r="X201" s="6">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="202" spans="1:24" ht="15.75">
+      <c r="Y201" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="202" spans="1:25" ht="15.75">
       <c r="A202" s="3">
         <v>5</v>
       </c>
@@ -14462,8 +15080,11 @@
       <c r="X202" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:24" ht="15.75">
+      <c r="Y202" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="203" spans="1:25" ht="15.75">
       <c r="A203" s="3">
         <v>5</v>
       </c>
@@ -14533,8 +15154,11 @@
       <c r="X203" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="204" spans="1:24" ht="15.75">
+      <c r="Y203" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="204" spans="1:25" ht="15.75">
       <c r="A204" s="3">
         <v>5</v>
       </c>
@@ -14604,8 +15228,11 @@
       <c r="X204" s="6">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="205" spans="1:24" ht="15.75">
+      <c r="Y204" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="205" spans="1:25" ht="15.75">
       <c r="A205" s="3">
         <v>5</v>
       </c>
@@ -14675,8 +15302,11 @@
       <c r="X205" s="6">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="206" spans="1:24" ht="15.75">
+      <c r="Y205" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="206" spans="1:25" ht="15.75">
       <c r="A206" s="3">
         <v>5</v>
       </c>
@@ -14746,8 +15376,11 @@
       <c r="X206" s="6">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="207" spans="1:24" ht="15.75">
+      <c r="Y206" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="207" spans="1:25" ht="15.75">
       <c r="A207" s="3">
         <v>5</v>
       </c>
@@ -14817,8 +15450,11 @@
       <c r="X207" s="6">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="208" spans="1:24" ht="15.75">
+      <c r="Y207" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="208" spans="1:25" ht="15.75">
       <c r="A208" s="3">
         <v>5</v>
       </c>
@@ -14888,8 +15524,11 @@
       <c r="X208" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="209" spans="1:24" ht="15.75">
+      <c r="Y208" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="209" spans="1:25" ht="15.75">
       <c r="A209" s="3">
         <v>5</v>
       </c>
@@ -14959,8 +15598,11 @@
       <c r="X209" s="6">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="210" spans="1:24" ht="15.75">
+      <c r="Y209" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="210" spans="1:25" ht="15.75">
       <c r="A210" s="3">
         <v>5</v>
       </c>
@@ -15030,8 +15672,11 @@
       <c r="X210" s="6">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="211" spans="1:24" ht="15.75">
+      <c r="Y210" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="211" spans="1:25" ht="15.75">
       <c r="A211" s="3">
         <v>5</v>
       </c>
@@ -15101,8 +15746,11 @@
       <c r="X211" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="212" spans="1:24" ht="15.75">
+      <c r="Y211" s="13">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="212" spans="1:25" ht="15.75">
       <c r="A212" s="3">
         <v>6</v>
       </c>
@@ -15168,8 +15816,11 @@
       <c r="V212" s="6"/>
       <c r="W212" s="6"/>
       <c r="X212" s="6"/>
-    </row>
-    <row r="213" spans="1:24" ht="15.75">
+      <c r="Y212" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="213" spans="1:25" ht="15.75">
       <c r="A213" s="3">
         <v>6</v>
       </c>
@@ -15235,8 +15886,11 @@
       <c r="V213" s="6"/>
       <c r="W213" s="6"/>
       <c r="X213" s="6"/>
-    </row>
-    <row r="214" spans="1:24" ht="15.75">
+      <c r="Y213" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="214" spans="1:25" ht="15.75">
       <c r="A214" s="3">
         <v>6</v>
       </c>
@@ -15302,8 +15956,11 @@
       <c r="V214" s="6"/>
       <c r="W214" s="6"/>
       <c r="X214" s="6"/>
-    </row>
-    <row r="215" spans="1:24" ht="15.75">
+      <c r="Y214" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="215" spans="1:25" ht="15.75">
       <c r="A215" s="3">
         <v>6</v>
       </c>
@@ -15369,8 +16026,11 @@
       <c r="V215" s="6"/>
       <c r="W215" s="6"/>
       <c r="X215" s="6"/>
-    </row>
-    <row r="216" spans="1:24" ht="15.75">
+      <c r="Y215" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="216" spans="1:25" ht="15.75">
       <c r="A216" s="3">
         <v>6</v>
       </c>
@@ -15436,8 +16096,11 @@
       <c r="V216" s="6"/>
       <c r="W216" s="6"/>
       <c r="X216" s="6"/>
-    </row>
-    <row r="217" spans="1:24" ht="15.75">
+      <c r="Y216" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="217" spans="1:25" ht="15.75">
       <c r="A217" s="3">
         <v>6</v>
       </c>
@@ -15503,8 +16166,11 @@
       <c r="V217" s="6"/>
       <c r="W217" s="6"/>
       <c r="X217" s="6"/>
-    </row>
-    <row r="218" spans="1:24" ht="15.75">
+      <c r="Y217" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="218" spans="1:25" ht="15.75">
       <c r="A218" s="3">
         <v>6</v>
       </c>
@@ -15570,8 +16236,11 @@
       <c r="V218" s="6"/>
       <c r="W218" s="6"/>
       <c r="X218" s="6"/>
-    </row>
-    <row r="219" spans="1:24" ht="15.75">
+      <c r="Y218" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="219" spans="1:25" ht="15.75">
       <c r="A219" s="3">
         <v>6</v>
       </c>
@@ -15637,8 +16306,11 @@
       <c r="V219" s="6"/>
       <c r="W219" s="6"/>
       <c r="X219" s="6"/>
-    </row>
-    <row r="220" spans="1:24" ht="15.75">
+      <c r="Y219" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="220" spans="1:25" ht="15.75">
       <c r="A220" s="3">
         <v>6</v>
       </c>
@@ -15704,8 +16376,11 @@
       <c r="V220" s="6"/>
       <c r="W220" s="6"/>
       <c r="X220" s="6"/>
-    </row>
-    <row r="221" spans="1:24" ht="15.75">
+      <c r="Y220" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="221" spans="1:25" ht="15.75">
       <c r="A221" s="3">
         <v>6</v>
       </c>
@@ -15771,8 +16446,11 @@
       <c r="V221" s="6"/>
       <c r="W221" s="6"/>
       <c r="X221" s="6"/>
-    </row>
-    <row r="222" spans="1:24" ht="15.75">
+      <c r="Y221" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="222" spans="1:25" ht="15.75">
       <c r="A222" s="3">
         <v>6</v>
       </c>
@@ -15838,8 +16516,11 @@
       <c r="V222" s="6"/>
       <c r="W222" s="6"/>
       <c r="X222" s="6"/>
-    </row>
-    <row r="223" spans="1:24" ht="15.75">
+      <c r="Y222" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="223" spans="1:25" ht="15.75">
       <c r="A223" s="3">
         <v>6</v>
       </c>
@@ -15905,8 +16586,11 @@
       <c r="V223" s="6"/>
       <c r="W223" s="6"/>
       <c r="X223" s="6"/>
-    </row>
-    <row r="224" spans="1:24" ht="15.75">
+      <c r="Y223" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="224" spans="1:25" ht="15.75">
       <c r="A224" s="3">
         <v>6</v>
       </c>
@@ -15972,8 +16656,11 @@
       <c r="V224" s="6"/>
       <c r="W224" s="6"/>
       <c r="X224" s="6"/>
-    </row>
-    <row r="225" spans="1:24" ht="15.75">
+      <c r="Y224" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="225" spans="1:25" ht="15.75">
       <c r="A225" s="3">
         <v>6</v>
       </c>
@@ -16039,8 +16726,11 @@
       <c r="V225" s="6"/>
       <c r="W225" s="6"/>
       <c r="X225" s="6"/>
-    </row>
-    <row r="226" spans="1:24" ht="15.75">
+      <c r="Y225" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="226" spans="1:25" ht="15.75">
       <c r="A226" s="3">
         <v>6</v>
       </c>
@@ -16106,8 +16796,11 @@
       <c r="V226" s="6"/>
       <c r="W226" s="6"/>
       <c r="X226" s="6"/>
-    </row>
-    <row r="227" spans="1:24" ht="15.75">
+      <c r="Y226" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="227" spans="1:25" ht="15.75">
       <c r="A227" s="3">
         <v>6</v>
       </c>
@@ -16173,8 +16866,11 @@
       <c r="V227" s="6"/>
       <c r="W227" s="6"/>
       <c r="X227" s="6"/>
-    </row>
-    <row r="228" spans="1:24" ht="15.75">
+      <c r="Y227" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="228" spans="1:25" ht="15.75">
       <c r="A228" s="3">
         <v>6</v>
       </c>
@@ -16240,8 +16936,11 @@
       <c r="V228" s="6"/>
       <c r="W228" s="6"/>
       <c r="X228" s="6"/>
-    </row>
-    <row r="229" spans="1:24" ht="15.75">
+      <c r="Y228" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="229" spans="1:25" ht="15.75">
       <c r="A229" s="3">
         <v>6</v>
       </c>
@@ -16307,8 +17006,11 @@
       <c r="V229" s="6"/>
       <c r="W229" s="6"/>
       <c r="X229" s="6"/>
-    </row>
-    <row r="230" spans="1:24" ht="15.75">
+      <c r="Y229" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="230" spans="1:25" ht="15.75">
       <c r="A230" s="3">
         <v>6</v>
       </c>
@@ -16374,8 +17076,11 @@
       <c r="V230" s="6"/>
       <c r="W230" s="6"/>
       <c r="X230" s="6"/>
-    </row>
-    <row r="231" spans="1:24" ht="15.75">
+      <c r="Y230" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="231" spans="1:25" ht="15.75">
       <c r="A231" s="3">
         <v>6</v>
       </c>
@@ -16445,8 +17150,11 @@
       <c r="X231" s="6">
         <v>1.00013</v>
       </c>
-    </row>
-    <row r="232" spans="1:24" ht="15.75">
+      <c r="Y231" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="232" spans="1:25" ht="15.75">
       <c r="A232" s="3">
         <v>6</v>
       </c>
@@ -16516,8 +17224,11 @@
       <c r="X232" s="6">
         <v>0.59992000000000001</v>
       </c>
-    </row>
-    <row r="233" spans="1:24" ht="15.75">
+      <c r="Y232" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="233" spans="1:25" ht="15.75">
       <c r="A233" s="3">
         <v>6</v>
       </c>
@@ -16587,8 +17298,11 @@
       <c r="X233" s="6">
         <v>0.40017000000000003</v>
       </c>
-    </row>
-    <row r="234" spans="1:24" ht="15.75">
+      <c r="Y233" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="234" spans="1:25" ht="15.75">
       <c r="A234" s="3">
         <v>6</v>
       </c>
@@ -16658,8 +17372,11 @@
       <c r="X234" s="6">
         <v>0.20113</v>
       </c>
-    </row>
-    <row r="235" spans="1:24" ht="15.75">
+      <c r="Y234" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="235" spans="1:25" ht="15.75">
       <c r="A235" s="3">
         <v>6</v>
       </c>
@@ -16729,8 +17446,11 @@
       <c r="X235" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="236" spans="1:24" ht="15.75">
+      <c r="Y235" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="236" spans="1:25" ht="15.75">
       <c r="A236" s="3">
         <v>6</v>
       </c>
@@ -16800,8 +17520,11 @@
       <c r="X236" s="6">
         <v>0.40012999999999999</v>
       </c>
-    </row>
-    <row r="237" spans="1:24" ht="15.75">
+      <c r="Y236" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="237" spans="1:25" ht="15.75">
       <c r="A237" s="3">
         <v>6</v>
       </c>
@@ -16871,8 +17594,11 @@
       <c r="X237" s="6">
         <v>0.12002</v>
       </c>
-    </row>
-    <row r="238" spans="1:24" ht="15.75">
+      <c r="Y237" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="238" spans="1:25" ht="15.75">
       <c r="A238" s="3">
         <v>6</v>
       </c>
@@ -16942,8 +17668,11 @@
       <c r="X238" s="6">
         <v>0.14974000000000001</v>
       </c>
-    </row>
-    <row r="239" spans="1:24" ht="15.75">
+      <c r="Y238" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="239" spans="1:25" ht="15.75">
       <c r="A239" s="3">
         <v>6</v>
       </c>
@@ -17013,8 +17742,11 @@
       <c r="X239" s="6">
         <v>1.9998400000000001</v>
       </c>
-    </row>
-    <row r="240" spans="1:24" ht="15.75">
+      <c r="Y239" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="240" spans="1:25" ht="15.75">
       <c r="A240" s="3">
         <v>6</v>
       </c>
@@ -17084,8 +17816,11 @@
       <c r="X240" s="6">
         <v>0.99990000000000001</v>
       </c>
-    </row>
-    <row r="241" spans="1:24" ht="15.75">
+      <c r="Y240" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="241" spans="1:25" ht="15.75">
       <c r="A241" s="3">
         <v>6</v>
       </c>
@@ -17155,8 +17890,11 @@
       <c r="X241" s="6">
         <v>0.60007999999999995</v>
       </c>
-    </row>
-    <row r="242" spans="1:24" ht="15.75">
+      <c r="Y241" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="242" spans="1:25" ht="15.75">
       <c r="A242" s="3">
         <v>6</v>
       </c>
@@ -17226,8 +17964,11 @@
       <c r="X242" s="6">
         <v>0.14915999999999999</v>
       </c>
-    </row>
-    <row r="243" spans="1:24" ht="15.75">
+      <c r="Y242" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="243" spans="1:25" ht="15.75">
       <c r="A243" s="3">
         <v>6</v>
       </c>
@@ -17297,8 +18038,11 @@
       <c r="X243" s="6">
         <v>4.0004900000000001</v>
       </c>
-    </row>
-    <row r="244" spans="1:24" ht="15.75">
+      <c r="Y243" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="244" spans="1:25" ht="15.75">
       <c r="A244" s="3">
         <v>6</v>
       </c>
@@ -17368,8 +18112,11 @@
       <c r="X244" s="6">
         <v>4.0005600000000001</v>
       </c>
-    </row>
-    <row r="245" spans="1:24" ht="15.75">
+      <c r="Y244" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="245" spans="1:25" ht="15.75">
       <c r="A245" s="3">
         <v>6</v>
       </c>
@@ -17377,7 +18124,7 @@
         <v>19</v>
       </c>
       <c r="C245" s="5">
-        <f t="shared" ref="C231:C245" si="5">100-SUM(D245:N245)</f>
+        <f t="shared" ref="C245" si="5">100-SUM(D245:N245)</f>
         <v>87.911199999999994</v>
       </c>
       <c r="D245" s="2">
@@ -17439,8 +18186,11 @@
       <c r="X245" s="6">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="246" spans="1:24" ht="15.75">
+      <c r="Y245" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="246" spans="1:25" ht="15.75">
       <c r="A246" s="3">
         <v>7</v>
       </c>
@@ -17506,8 +18256,11 @@
       <c r="V246" s="6"/>
       <c r="W246" s="6"/>
       <c r="X246" s="6"/>
-    </row>
-    <row r="247" spans="1:24" ht="15.75">
+      <c r="Y246" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="247" spans="1:25" ht="15.75">
       <c r="A247" s="3">
         <v>7</v>
       </c>
@@ -17573,8 +18326,11 @@
       <c r="V247" s="6"/>
       <c r="W247" s="6"/>
       <c r="X247" s="6"/>
-    </row>
-    <row r="248" spans="1:24" ht="15.75">
+      <c r="Y247" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="248" spans="1:25" ht="15.75">
       <c r="A248" s="3">
         <v>7</v>
       </c>
@@ -17640,8 +18396,11 @@
       <c r="V248" s="6"/>
       <c r="W248" s="6"/>
       <c r="X248" s="6"/>
-    </row>
-    <row r="249" spans="1:24" ht="15.75">
+      <c r="Y248" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="249" spans="1:25" ht="15.75">
       <c r="A249" s="3">
         <v>7</v>
       </c>
@@ -17707,8 +18466,11 @@
       <c r="V249" s="6"/>
       <c r="W249" s="6"/>
       <c r="X249" s="6"/>
-    </row>
-    <row r="250" spans="1:24" ht="15.75">
+      <c r="Y249" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="250" spans="1:25" ht="15.75">
       <c r="A250" s="3">
         <v>7</v>
       </c>
@@ -17774,8 +18536,11 @@
       <c r="V250" s="6"/>
       <c r="W250" s="6"/>
       <c r="X250" s="6"/>
-    </row>
-    <row r="251" spans="1:24" ht="15.75">
+      <c r="Y250" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="251" spans="1:25" ht="15.75">
       <c r="A251" s="3">
         <v>7</v>
       </c>
@@ -17841,8 +18606,11 @@
       <c r="V251" s="6"/>
       <c r="W251" s="6"/>
       <c r="X251" s="6"/>
-    </row>
-    <row r="252" spans="1:24" ht="15.75">
+      <c r="Y251" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="252" spans="1:25" ht="15.75">
       <c r="A252" s="3">
         <v>7</v>
       </c>
@@ -17908,8 +18676,11 @@
       <c r="V252" s="6"/>
       <c r="W252" s="6"/>
       <c r="X252" s="6"/>
-    </row>
-    <row r="253" spans="1:24" ht="15.75">
+      <c r="Y252" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="253" spans="1:25" ht="15.75">
       <c r="A253" s="3">
         <v>7</v>
       </c>
@@ -17975,8 +18746,11 @@
       <c r="V253" s="6"/>
       <c r="W253" s="6"/>
       <c r="X253" s="6"/>
-    </row>
-    <row r="254" spans="1:24" ht="15.75">
+      <c r="Y253" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="254" spans="1:25" ht="15.75">
       <c r="A254" s="3">
         <v>7</v>
       </c>
@@ -18042,8 +18816,11 @@
       <c r="V254" s="6"/>
       <c r="W254" s="6"/>
       <c r="X254" s="6"/>
-    </row>
-    <row r="255" spans="1:24" ht="15.75">
+      <c r="Y254" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="255" spans="1:25" ht="15.75">
       <c r="A255" s="3">
         <v>7</v>
       </c>
@@ -18109,8 +18886,11 @@
       <c r="V255" s="6"/>
       <c r="W255" s="6"/>
       <c r="X255" s="6"/>
-    </row>
-    <row r="256" spans="1:24" ht="15.75">
+      <c r="Y255" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="256" spans="1:25" ht="15.75">
       <c r="A256" s="3">
         <v>7</v>
       </c>
@@ -18176,8 +18956,11 @@
       <c r="V256" s="6"/>
       <c r="W256" s="6"/>
       <c r="X256" s="6"/>
-    </row>
-    <row r="257" spans="1:24" ht="15.75">
+      <c r="Y256" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="257" spans="1:25" ht="15.75">
       <c r="A257" s="3">
         <v>7</v>
       </c>
@@ -18243,8 +19026,11 @@
       <c r="V257" s="6"/>
       <c r="W257" s="6"/>
       <c r="X257" s="6"/>
-    </row>
-    <row r="258" spans="1:24" ht="15.75">
+      <c r="Y257" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="258" spans="1:25" ht="15.75">
       <c r="A258" s="3">
         <v>7</v>
       </c>
@@ -18310,8 +19096,11 @@
       <c r="V258" s="6"/>
       <c r="W258" s="6"/>
       <c r="X258" s="6"/>
-    </row>
-    <row r="259" spans="1:24" ht="15.75">
+      <c r="Y258" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="259" spans="1:25" ht="15.75">
       <c r="A259" s="3">
         <v>7</v>
       </c>
@@ -18377,8 +19166,11 @@
       <c r="V259" s="6"/>
       <c r="W259" s="6"/>
       <c r="X259" s="6"/>
-    </row>
-    <row r="260" spans="1:24" ht="15.75">
+      <c r="Y259" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="260" spans="1:25" ht="15.75">
       <c r="A260" s="3">
         <v>7</v>
       </c>
@@ -18444,8 +19236,11 @@
       <c r="V260" s="6"/>
       <c r="W260" s="6"/>
       <c r="X260" s="6"/>
-    </row>
-    <row r="261" spans="1:24" ht="15.75">
+      <c r="Y260" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="261" spans="1:25" ht="15.75">
       <c r="A261" s="3">
         <v>7</v>
       </c>
@@ -18511,8 +19306,11 @@
       <c r="V261" s="6"/>
       <c r="W261" s="6"/>
       <c r="X261" s="6"/>
-    </row>
-    <row r="262" spans="1:24" ht="15.75">
+      <c r="Y261" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="262" spans="1:25" ht="15.75">
       <c r="A262" s="3">
         <v>7</v>
       </c>
@@ -18578,8 +19376,11 @@
       <c r="V262" s="6"/>
       <c r="W262" s="6"/>
       <c r="X262" s="6"/>
-    </row>
-    <row r="263" spans="1:24" ht="15.75">
+      <c r="Y262" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="263" spans="1:25" ht="15.75">
       <c r="A263" s="3">
         <v>7</v>
       </c>
@@ -18645,8 +19446,11 @@
       <c r="V263" s="6"/>
       <c r="W263" s="6"/>
       <c r="X263" s="6"/>
-    </row>
-    <row r="264" spans="1:24" ht="15.75">
+      <c r="Y263" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="264" spans="1:25" ht="15.75">
       <c r="A264" s="3">
         <v>7</v>
       </c>
@@ -18712,8 +19516,11 @@
       <c r="V264" s="6"/>
       <c r="W264" s="6"/>
       <c r="X264" s="6"/>
-    </row>
-    <row r="265" spans="1:24" ht="15.75">
+      <c r="Y264" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="265" spans="1:25" ht="15.75">
       <c r="A265" s="3">
         <v>7</v>
       </c>
@@ -18783,8 +19590,11 @@
       <c r="X265" s="6">
         <v>0.59997</v>
       </c>
-    </row>
-    <row r="266" spans="1:24" ht="15.75">
+      <c r="Y265" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="266" spans="1:25" ht="15.75">
       <c r="A266" s="3">
         <v>7</v>
       </c>
@@ -18854,8 +19664,11 @@
       <c r="X266" s="6">
         <v>0.39977000000000001</v>
       </c>
-    </row>
-    <row r="267" spans="1:24" ht="15.75">
+      <c r="Y266" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="267" spans="1:25" ht="15.75">
       <c r="A267" s="3">
         <v>7</v>
       </c>
@@ -18925,8 +19738,11 @@
       <c r="X267" s="6">
         <v>1.00007</v>
       </c>
-    </row>
-    <row r="268" spans="1:24" ht="15.75">
+      <c r="Y267" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="268" spans="1:25" ht="15.75">
       <c r="A268" s="3">
         <v>7</v>
       </c>
@@ -18996,8 +19812,11 @@
       <c r="X268" s="6">
         <v>1.0000500000000001</v>
       </c>
-    </row>
-    <row r="269" spans="1:24" ht="15.75">
+      <c r="Y268" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="269" spans="1:25" ht="15.75">
       <c r="A269" s="3">
         <v>7</v>
       </c>
@@ -19067,8 +19886,11 @@
       <c r="X269" s="6">
         <v>0.14976</v>
       </c>
-    </row>
-    <row r="270" spans="1:24" ht="15.75">
+      <c r="Y269" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="270" spans="1:25" ht="15.75">
       <c r="A270" s="3">
         <v>7</v>
       </c>
@@ -19138,8 +19960,11 @@
       <c r="X270" s="6">
         <v>0.60006000000000004</v>
       </c>
-    </row>
-    <row r="271" spans="1:24" ht="15.75">
+      <c r="Y270" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="271" spans="1:25" ht="15.75">
       <c r="A271" s="3">
         <v>7</v>
       </c>
@@ -19209,8 +20034,11 @@
       <c r="X271" s="6">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="272" spans="1:24" ht="15.75">
+      <c r="Y271" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="272" spans="1:25" ht="15.75">
       <c r="A272" s="3">
         <v>7</v>
       </c>
@@ -19280,8 +20108,11 @@
       <c r="X272" s="6">
         <v>0.20008000000000001</v>
       </c>
-    </row>
-    <row r="273" spans="1:24" ht="15.75">
+      <c r="Y272" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="273" spans="1:25" ht="15.75">
       <c r="A273" s="3">
         <v>7</v>
       </c>
@@ -19351,8 +20182,11 @@
       <c r="X273" s="6">
         <v>2.0011899999999998</v>
       </c>
-    </row>
-    <row r="274" spans="1:24" ht="15.75">
+      <c r="Y273" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="274" spans="1:25" ht="15.75">
       <c r="A274" s="3">
         <v>7</v>
       </c>
@@ -19422,8 +20256,11 @@
       <c r="X274" s="6">
         <v>0.39995999999999998</v>
       </c>
-    </row>
-    <row r="275" spans="1:24" ht="15.75">
+      <c r="Y274" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="275" spans="1:25" ht="15.75">
       <c r="A275" s="3">
         <v>7</v>
       </c>
@@ -19493,8 +20330,11 @@
       <c r="X275" s="6">
         <v>2.0004900000000001</v>
       </c>
-    </row>
-    <row r="276" spans="1:24" ht="15.75">
+      <c r="Y275" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="276" spans="1:25" ht="15.75">
       <c r="A276" s="3">
         <v>7</v>
       </c>
@@ -19564,8 +20404,11 @@
       <c r="X276" s="6">
         <v>0.15004999999999999</v>
       </c>
-    </row>
-    <row r="277" spans="1:24" ht="15.75">
+      <c r="Y276" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="277" spans="1:25" ht="15.75">
       <c r="A277" s="3">
         <v>7</v>
       </c>
@@ -19635,8 +20478,11 @@
       <c r="X277" s="6">
         <v>0.12016</v>
       </c>
-    </row>
-    <row r="278" spans="1:24" ht="15.75">
+      <c r="Y277" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="278" spans="1:25" ht="15.75">
       <c r="A278" s="3">
         <v>7</v>
       </c>
@@ -19706,8 +20552,11 @@
       <c r="X278" s="6">
         <v>0.12016</v>
       </c>
-    </row>
-    <row r="279" spans="1:24" ht="15.75">
+      <c r="Y278" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="279" spans="1:25" ht="15.75">
       <c r="A279" s="3">
         <v>7</v>
       </c>
@@ -19777,8 +20626,11 @@
       <c r="X279" s="6">
         <v>9.9860000000000004E-2</v>
       </c>
-    </row>
-    <row r="280" spans="1:24" ht="15.75">
+      <c r="Y279" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="280" spans="1:25" ht="15.75">
       <c r="A280" s="3">
         <v>8</v>
       </c>
@@ -19844,8 +20696,11 @@
       <c r="V280" s="6"/>
       <c r="W280" s="6"/>
       <c r="X280" s="6"/>
-    </row>
-    <row r="281" spans="1:24" ht="15.75">
+      <c r="Y280" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:25" ht="15.75">
       <c r="A281" s="3">
         <v>8</v>
       </c>
@@ -19911,8 +20766,11 @@
       <c r="V281" s="6"/>
       <c r="W281" s="6"/>
       <c r="X281" s="6"/>
-    </row>
-    <row r="282" spans="1:24" ht="15.75">
+      <c r="Y281" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:25" ht="15.75">
       <c r="A282" s="3">
         <v>8</v>
       </c>
@@ -19978,8 +20836,11 @@
       <c r="V282" s="6"/>
       <c r="W282" s="6"/>
       <c r="X282" s="6"/>
-    </row>
-    <row r="283" spans="1:24" ht="15.75">
+      <c r="Y282" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:25" ht="15.75">
       <c r="A283" s="3">
         <v>8</v>
       </c>
@@ -20045,8 +20906,11 @@
       <c r="V283" s="6"/>
       <c r="W283" s="6"/>
       <c r="X283" s="6"/>
-    </row>
-    <row r="284" spans="1:24" ht="15.75">
+      <c r="Y283" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="284" spans="1:25" ht="15.75">
       <c r="A284" s="3">
         <v>8</v>
       </c>
@@ -20112,8 +20976,11 @@
       <c r="V284" s="6"/>
       <c r="W284" s="6"/>
       <c r="X284" s="6"/>
-    </row>
-    <row r="285" spans="1:24" ht="15.75">
+      <c r="Y284" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="285" spans="1:25" ht="15.75">
       <c r="A285" s="3">
         <v>8</v>
       </c>
@@ -20179,8 +21046,11 @@
       <c r="V285" s="6"/>
       <c r="W285" s="6"/>
       <c r="X285" s="6"/>
-    </row>
-    <row r="286" spans="1:24" ht="15.75">
+      <c r="Y285" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:25" ht="15.75">
       <c r="A286" s="3">
         <v>8</v>
       </c>
@@ -20246,8 +21116,11 @@
       <c r="V286" s="6"/>
       <c r="W286" s="6"/>
       <c r="X286" s="6"/>
-    </row>
-    <row r="287" spans="1:24" ht="15.75">
+      <c r="Y286" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="287" spans="1:25" ht="15.75">
       <c r="A287" s="3">
         <v>8</v>
       </c>
@@ -20313,8 +21186,11 @@
       <c r="V287" s="6"/>
       <c r="W287" s="6"/>
       <c r="X287" s="6"/>
-    </row>
-    <row r="288" spans="1:24" ht="15.75">
+      <c r="Y287" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="288" spans="1:25" ht="15.75">
       <c r="A288" s="3">
         <v>8</v>
       </c>
@@ -20380,8 +21256,11 @@
       <c r="V288" s="6"/>
       <c r="W288" s="6"/>
       <c r="X288" s="6"/>
-    </row>
-    <row r="289" spans="1:24" ht="15.75">
+      <c r="Y288" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="289" spans="1:25" ht="15.75">
       <c r="A289" s="3">
         <v>8</v>
       </c>
@@ -20447,8 +21326,11 @@
       <c r="V289" s="6"/>
       <c r="W289" s="6"/>
       <c r="X289" s="6"/>
-    </row>
-    <row r="290" spans="1:24" ht="15.75">
+      <c r="Y289" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="290" spans="1:25" ht="15.75">
       <c r="A290" s="3">
         <v>8</v>
       </c>
@@ -20514,8 +21396,11 @@
       <c r="V290" s="6"/>
       <c r="W290" s="6"/>
       <c r="X290" s="6"/>
-    </row>
-    <row r="291" spans="1:24" ht="15.75">
+      <c r="Y290" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="291" spans="1:25" ht="15.75">
       <c r="A291" s="3">
         <v>8</v>
       </c>
@@ -20581,8 +21466,11 @@
       <c r="V291" s="6"/>
       <c r="W291" s="6"/>
       <c r="X291" s="6"/>
-    </row>
-    <row r="292" spans="1:24" ht="15.75">
+      <c r="Y291" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="292" spans="1:25" ht="15.75">
       <c r="A292" s="3">
         <v>8</v>
       </c>
@@ -20648,8 +21536,11 @@
       <c r="V292" s="6"/>
       <c r="W292" s="6"/>
       <c r="X292" s="6"/>
-    </row>
-    <row r="293" spans="1:24" ht="15.75">
+      <c r="Y292" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="293" spans="1:25" ht="15.75">
       <c r="A293" s="3">
         <v>8</v>
       </c>
@@ -20715,8 +21606,11 @@
       <c r="V293" s="6"/>
       <c r="W293" s="6"/>
       <c r="X293" s="6"/>
-    </row>
-    <row r="294" spans="1:24" ht="15.75">
+      <c r="Y293" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="294" spans="1:25" ht="15.75">
       <c r="A294" s="3">
         <v>8</v>
       </c>
@@ -20782,8 +21676,11 @@
       <c r="V294" s="6"/>
       <c r="W294" s="6"/>
       <c r="X294" s="6"/>
-    </row>
-    <row r="295" spans="1:24" ht="15.75">
+      <c r="Y294" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="295" spans="1:25" ht="15.75">
       <c r="A295" s="3">
         <v>8</v>
       </c>
@@ -20849,8 +21746,11 @@
       <c r="V295" s="6"/>
       <c r="W295" s="6"/>
       <c r="X295" s="6"/>
-    </row>
-    <row r="296" spans="1:24" ht="15.75">
+      <c r="Y295" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="296" spans="1:25" ht="15.75">
       <c r="A296" s="3">
         <v>8</v>
       </c>
@@ -20916,8 +21816,11 @@
       <c r="V296" s="6"/>
       <c r="W296" s="6"/>
       <c r="X296" s="6"/>
-    </row>
-    <row r="297" spans="1:24" ht="15.75">
+      <c r="Y296" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="297" spans="1:25" ht="15.75">
       <c r="A297" s="3">
         <v>8</v>
       </c>
@@ -20983,8 +21886,11 @@
       <c r="V297" s="6"/>
       <c r="W297" s="6"/>
       <c r="X297" s="6"/>
-    </row>
-    <row r="298" spans="1:24" ht="15.75">
+      <c r="Y297" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="298" spans="1:25" ht="15.75">
       <c r="A298" s="3">
         <v>8</v>
       </c>
@@ -21050,8 +21956,11 @@
       <c r="V298" s="6"/>
       <c r="W298" s="6"/>
       <c r="X298" s="6"/>
-    </row>
-    <row r="299" spans="1:24" ht="15.75">
+      <c r="Y298" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="299" spans="1:25" ht="15.75">
       <c r="A299" s="3">
         <v>8</v>
       </c>
@@ -21117,8 +22026,11 @@
       <c r="V299" s="6"/>
       <c r="W299" s="6"/>
       <c r="X299" s="6"/>
-    </row>
-    <row r="300" spans="1:24" ht="15.75">
+      <c r="Y299" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="300" spans="1:25" ht="15.75">
       <c r="A300" s="3">
         <v>8</v>
       </c>
@@ -21188,8 +22100,11 @@
       <c r="X300" s="6">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="301" spans="1:24" ht="15.75">
+      <c r="Y300" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="301" spans="1:25" ht="15.75">
       <c r="A301" s="3">
         <v>8</v>
       </c>
@@ -21259,8 +22174,11 @@
       <c r="X301" s="6">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="302" spans="1:24" ht="15.75">
+      <c r="Y301" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="302" spans="1:25" ht="15.75">
       <c r="A302" s="3">
         <v>8</v>
       </c>
@@ -21330,8 +22248,11 @@
       <c r="X302" s="6">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="303" spans="1:24" ht="15.75">
+      <c r="Y302" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="303" spans="1:25" ht="15.75">
       <c r="A303" s="3">
         <v>8</v>
       </c>
@@ -21401,8 +22322,11 @@
       <c r="X303" s="6">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="304" spans="1:24" ht="15.75">
+      <c r="Y303" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="304" spans="1:25" ht="15.75">
       <c r="A304" s="3">
         <v>8</v>
       </c>
@@ -21472,8 +22396,11 @@
       <c r="X304" s="6">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="305" spans="1:24" ht="15.75">
+      <c r="Y304" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="305" spans="1:25" ht="15.75">
       <c r="A305" s="3">
         <v>8</v>
       </c>
@@ -21543,8 +22470,11 @@
       <c r="X305" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="306" spans="1:24" ht="15.75">
+      <c r="Y305" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="306" spans="1:25" ht="15.75">
       <c r="A306" s="3">
         <v>8</v>
       </c>
@@ -21614,8 +22544,11 @@
       <c r="X306" s="6">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="307" spans="1:24" ht="15.75">
+      <c r="Y306" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="307" spans="1:25" ht="15.75">
       <c r="A307" s="3">
         <v>8</v>
       </c>
@@ -21685,8 +22618,11 @@
       <c r="X307" s="6">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="308" spans="1:24" ht="15.75">
+      <c r="Y307" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="308" spans="1:25" ht="15.75">
       <c r="A308" s="3">
         <v>8</v>
       </c>
@@ -21756,8 +22692,11 @@
       <c r="X308" s="6">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="309" spans="1:24" ht="15.75">
+      <c r="Y308" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="309" spans="1:25" ht="15.75">
       <c r="A309" s="3">
         <v>8</v>
       </c>
@@ -21827,8 +22766,11 @@
       <c r="X309" s="6">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="310" spans="1:24" ht="15.75">
+      <c r="Y309" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="310" spans="1:25" ht="15.75">
       <c r="A310" s="3">
         <v>8</v>
       </c>
@@ -21898,8 +22840,11 @@
       <c r="X310" s="6">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="311" spans="1:24" ht="15.75">
+      <c r="Y310" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="311" spans="1:25" ht="15.75">
       <c r="A311" s="3">
         <v>8</v>
       </c>
@@ -21969,8 +22914,11 @@
       <c r="X311" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="312" spans="1:24" ht="15.75">
+      <c r="Y311" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="312" spans="1:25" ht="15.75">
       <c r="A312" s="3">
         <v>8</v>
       </c>
@@ -22040,8 +22988,11 @@
       <c r="X312" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="313" spans="1:24" ht="15.75">
+      <c r="Y312" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="313" spans="1:25" ht="15.75">
       <c r="A313" s="3">
         <v>8</v>
       </c>
@@ -22111,8 +23062,11 @@
       <c r="X313" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="314" spans="1:24" ht="15.75">
+      <c r="Y313" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="314" spans="1:25" ht="15.75">
       <c r="A314" s="3">
         <v>8</v>
       </c>
@@ -22182,8 +23136,11 @@
       <c r="X314" s="6">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="315" spans="1:24" ht="15.75">
+      <c r="Y314" s="13">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="315" spans="1:25" ht="15.75">
       <c r="A315" s="3">
         <v>10</v>
       </c>
@@ -22249,8 +23206,11 @@
       <c r="V315" s="6"/>
       <c r="W315" s="6"/>
       <c r="X315" s="6"/>
-    </row>
-    <row r="316" spans="1:24" ht="15.75">
+      <c r="Y315" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="316" spans="1:25" ht="15.75">
       <c r="A316" s="3">
         <v>10</v>
       </c>
@@ -22316,8 +23276,11 @@
       <c r="V316" s="6"/>
       <c r="W316" s="6"/>
       <c r="X316" s="6"/>
-    </row>
-    <row r="317" spans="1:24" ht="15.75">
+      <c r="Y316" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="317" spans="1:25" ht="15.75">
       <c r="A317" s="3">
         <v>10</v>
       </c>
@@ -22383,8 +23346,11 @@
       <c r="V317" s="6"/>
       <c r="W317" s="6"/>
       <c r="X317" s="6"/>
-    </row>
-    <row r="318" spans="1:24" ht="15.75">
+      <c r="Y317" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="318" spans="1:25" ht="15.75">
       <c r="A318" s="3">
         <v>10</v>
       </c>
@@ -22450,8 +23416,11 @@
       <c r="V318" s="6"/>
       <c r="W318" s="6"/>
       <c r="X318" s="6"/>
-    </row>
-    <row r="319" spans="1:24" ht="15.75">
+      <c r="Y318" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="319" spans="1:25" ht="15.75">
       <c r="A319" s="3">
         <v>10</v>
       </c>
@@ -22517,8 +23486,11 @@
       <c r="V319" s="6"/>
       <c r="W319" s="6"/>
       <c r="X319" s="6"/>
-    </row>
-    <row r="320" spans="1:24" ht="15.75">
+      <c r="Y319" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="320" spans="1:25" ht="15.75">
       <c r="A320" s="3">
         <v>10</v>
       </c>
@@ -22584,8 +23556,11 @@
       <c r="V320" s="6"/>
       <c r="W320" s="6"/>
       <c r="X320" s="6"/>
-    </row>
-    <row r="321" spans="1:24" ht="15.75">
+      <c r="Y320" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="321" spans="1:25" ht="15.75">
       <c r="A321" s="3">
         <v>10</v>
       </c>
@@ -22651,8 +23626,11 @@
       <c r="V321" s="6"/>
       <c r="W321" s="6"/>
       <c r="X321" s="6"/>
-    </row>
-    <row r="322" spans="1:24" ht="15.75">
+      <c r="Y321" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="322" spans="1:25" ht="15.75">
       <c r="A322" s="3">
         <v>10</v>
       </c>
@@ -22718,8 +23696,11 @@
       <c r="V322" s="6"/>
       <c r="W322" s="6"/>
       <c r="X322" s="6"/>
-    </row>
-    <row r="323" spans="1:24" ht="15.75">
+      <c r="Y322" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="323" spans="1:25" ht="15.75">
       <c r="A323" s="3">
         <v>10</v>
       </c>
@@ -22785,8 +23766,11 @@
       <c r="V323" s="6"/>
       <c r="W323" s="6"/>
       <c r="X323" s="6"/>
-    </row>
-    <row r="324" spans="1:24" ht="15.75">
+      <c r="Y323" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="324" spans="1:25" ht="15.75">
       <c r="A324" s="3">
         <v>10</v>
       </c>
@@ -22852,8 +23836,11 @@
       <c r="V324" s="6"/>
       <c r="W324" s="6"/>
       <c r="X324" s="6"/>
-    </row>
-    <row r="325" spans="1:24" ht="15.75">
+      <c r="Y324" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="325" spans="1:25" ht="15.75">
       <c r="A325" s="3">
         <v>10</v>
       </c>
@@ -22919,8 +23906,11 @@
       <c r="V325" s="6"/>
       <c r="W325" s="6"/>
       <c r="X325" s="6"/>
-    </row>
-    <row r="326" spans="1:24" ht="15.75">
+      <c r="Y325" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="326" spans="1:25" ht="15.75">
       <c r="A326" s="3">
         <v>10</v>
       </c>
@@ -22986,8 +23976,11 @@
       <c r="V326" s="6"/>
       <c r="W326" s="6"/>
       <c r="X326" s="6"/>
-    </row>
-    <row r="327" spans="1:24" ht="15.75">
+      <c r="Y326" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="327" spans="1:25" ht="15.75">
       <c r="A327" s="3">
         <v>10</v>
       </c>
@@ -23059,8 +24052,11 @@
       <c r="X327" s="6">
         <v>0.49834000000000001</v>
       </c>
-    </row>
-    <row r="328" spans="1:24" ht="15.75">
+      <c r="Y327" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="328" spans="1:25" ht="15.75">
       <c r="A328" s="3">
         <v>10</v>
       </c>
@@ -23132,8 +24128,11 @@
       <c r="X328" s="6">
         <v>0.41954999999999998</v>
       </c>
-    </row>
-    <row r="329" spans="1:24" ht="15.75">
+      <c r="Y328" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="329" spans="1:25" ht="15.75">
       <c r="A329" s="3">
         <v>10</v>
       </c>
@@ -23205,8 +24204,11 @@
       <c r="X329" s="6">
         <v>0.22856000000000001</v>
       </c>
-    </row>
-    <row r="330" spans="1:24" ht="15.75">
+      <c r="Y329" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="330" spans="1:25" ht="15.75">
       <c r="A330" s="3">
         <v>10</v>
       </c>
@@ -23278,8 +24280,11 @@
       <c r="X330" s="6">
         <v>0.35367999999999999</v>
       </c>
-    </row>
-    <row r="331" spans="1:24" ht="15.75">
+      <c r="Y330" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="331" spans="1:25" ht="15.75">
       <c r="A331" s="3">
         <v>10</v>
       </c>
@@ -23351,8 +24356,11 @@
       <c r="X331" s="6">
         <v>0.27274999999999999</v>
       </c>
-    </row>
-    <row r="332" spans="1:24" ht="15.75">
+      <c r="Y331" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="332" spans="1:25" ht="15.75">
       <c r="A332" s="3">
         <v>10</v>
       </c>
@@ -23424,8 +24432,11 @@
       <c r="X332" s="6">
         <v>0.29698999999999998</v>
       </c>
-    </row>
-    <row r="333" spans="1:24" ht="15.75">
+      <c r="Y332" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="333" spans="1:25" ht="15.75">
       <c r="A333" s="3">
         <v>10</v>
       </c>
@@ -23497,8 +24508,11 @@
       <c r="X333" s="6">
         <v>0.24962000000000001</v>
       </c>
-    </row>
-    <row r="334" spans="1:24" ht="15.75">
+      <c r="Y333" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="334" spans="1:25" ht="15.75">
       <c r="A334" s="3">
         <v>10</v>
       </c>
@@ -23570,8 +24584,11 @@
       <c r="X334" s="6">
         <v>0.21024000000000001</v>
       </c>
-    </row>
-    <row r="335" spans="1:24" ht="15.75">
+      <c r="Y334" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="335" spans="1:25" ht="15.75">
       <c r="A335" s="3">
         <v>10</v>
       </c>
@@ -23643,8 +24660,11 @@
       <c r="X335" s="6">
         <v>0.19288</v>
       </c>
-    </row>
-    <row r="336" spans="1:24" ht="15.75">
+      <c r="Y335" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="336" spans="1:25" ht="15.75">
       <c r="A336" s="3">
         <v>10</v>
       </c>
@@ -23716,8 +24736,11 @@
       <c r="X336" s="6">
         <v>0.17693</v>
       </c>
-    </row>
-    <row r="337" spans="1:24" ht="15.75">
+      <c r="Y336" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="337" spans="1:25" ht="15.75">
       <c r="A337" s="3">
         <v>10</v>
       </c>
@@ -23789,8 +24812,11 @@
       <c r="X337" s="6">
         <v>0.14879000000000001</v>
       </c>
-    </row>
-    <row r="338" spans="1:24" ht="15.75">
+      <c r="Y337" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="338" spans="1:25" ht="15.75">
       <c r="A338" s="3">
         <v>10</v>
       </c>
@@ -23862,8 +24888,11 @@
       <c r="X338" s="6">
         <v>0.16188</v>
       </c>
-    </row>
-    <row r="339" spans="1:24" ht="15.75">
+      <c r="Y338" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="339" spans="1:25" ht="15.75">
       <c r="A339" s="3">
         <v>10</v>
       </c>
@@ -23935,8 +24964,11 @@
       <c r="X339" s="6">
         <v>0.13558999999999999</v>
       </c>
-    </row>
-    <row r="340" spans="1:24" ht="15.75">
+      <c r="Y339" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="340" spans="1:25" ht="15.75">
       <c r="A340" s="3">
         <v>10</v>
       </c>
@@ -24008,8 +25040,11 @@
       <c r="X340" s="6">
         <v>0.11534</v>
       </c>
-    </row>
-    <row r="341" spans="1:24" ht="15.75">
+      <c r="Y340" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="341" spans="1:25" ht="15.75">
       <c r="A341" s="3">
         <v>10</v>
       </c>
@@ -24081,8 +25116,11 @@
       <c r="X341" s="6">
         <v>0.1249</v>
       </c>
-    </row>
-    <row r="342" spans="1:24" ht="15.75">
+      <c r="Y341" s="13">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="342" spans="1:25" ht="15.75">
       <c r="A342" s="3">
         <v>11</v>
       </c>
@@ -24148,8 +25186,11 @@
       <c r="V342" s="6"/>
       <c r="W342" s="6"/>
       <c r="X342" s="6"/>
-    </row>
-    <row r="343" spans="1:24" ht="15.75">
+      <c r="Y342" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="343" spans="1:25" ht="15.75">
       <c r="A343" s="3">
         <v>11</v>
       </c>
@@ -24215,8 +25256,11 @@
       <c r="V343" s="6"/>
       <c r="W343" s="6"/>
       <c r="X343" s="6"/>
-    </row>
-    <row r="344" spans="1:24" ht="15.75">
+      <c r="Y343" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="344" spans="1:25" ht="15.75">
       <c r="A344" s="3">
         <v>11</v>
       </c>
@@ -24282,8 +25326,11 @@
       <c r="V344" s="6"/>
       <c r="W344" s="6"/>
       <c r="X344" s="6"/>
-    </row>
-    <row r="345" spans="1:24" ht="15.75">
+      <c r="Y344" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="345" spans="1:25" ht="15.75">
       <c r="A345" s="3">
         <v>11</v>
       </c>
@@ -24349,8 +25396,11 @@
       <c r="V345" s="6"/>
       <c r="W345" s="6"/>
       <c r="X345" s="6"/>
-    </row>
-    <row r="346" spans="1:24" ht="15.75">
+      <c r="Y345" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="346" spans="1:25" ht="15.75">
       <c r="A346" s="3">
         <v>11</v>
       </c>
@@ -24416,8 +25466,11 @@
       <c r="V346" s="6"/>
       <c r="W346" s="6"/>
       <c r="X346" s="6"/>
-    </row>
-    <row r="347" spans="1:24" ht="15.75">
+      <c r="Y346" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="347" spans="1:25" ht="15.75">
       <c r="A347" s="3">
         <v>11</v>
       </c>
@@ -24483,8 +25536,11 @@
       <c r="V347" s="6"/>
       <c r="W347" s="6"/>
       <c r="X347" s="6"/>
-    </row>
-    <row r="348" spans="1:24" ht="15.75">
+      <c r="Y347" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="348" spans="1:25" ht="15.75">
       <c r="A348" s="3">
         <v>11</v>
       </c>
@@ -24550,8 +25606,11 @@
       <c r="V348" s="6"/>
       <c r="W348" s="6"/>
       <c r="X348" s="6"/>
-    </row>
-    <row r="349" spans="1:24" ht="15.75">
+      <c r="Y348" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="349" spans="1:25" ht="15.75">
       <c r="A349" s="3">
         <v>11</v>
       </c>
@@ -24617,8 +25676,11 @@
       <c r="V349" s="6"/>
       <c r="W349" s="6"/>
       <c r="X349" s="6"/>
-    </row>
-    <row r="350" spans="1:24" ht="15.75">
+      <c r="Y349" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="350" spans="1:25" ht="15.75">
       <c r="A350" s="3">
         <v>11</v>
       </c>
@@ -24684,8 +25746,11 @@
       <c r="V350" s="6"/>
       <c r="W350" s="6"/>
       <c r="X350" s="6"/>
-    </row>
-    <row r="351" spans="1:24" ht="15.75">
+      <c r="Y350" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="351" spans="1:25" ht="15.75">
       <c r="A351" s="3">
         <v>11</v>
       </c>
@@ -24751,8 +25816,11 @@
       <c r="V351" s="6"/>
       <c r="W351" s="6"/>
       <c r="X351" s="6"/>
-    </row>
-    <row r="352" spans="1:24" ht="15.75">
+      <c r="Y351" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="352" spans="1:25" ht="15.75">
       <c r="A352" s="3">
         <v>11</v>
       </c>
@@ -24818,8 +25886,11 @@
       <c r="V352" s="6"/>
       <c r="W352" s="6"/>
       <c r="X352" s="6"/>
-    </row>
-    <row r="353" spans="1:24" ht="15.75">
+      <c r="Y352" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="353" spans="1:25" ht="15.75">
       <c r="A353" s="3">
         <v>11</v>
       </c>
@@ -24885,8 +25956,11 @@
       <c r="V353" s="6"/>
       <c r="W353" s="6"/>
       <c r="X353" s="6"/>
-    </row>
-    <row r="354" spans="1:24" ht="15.75">
+      <c r="Y353" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="354" spans="1:25" ht="15.75">
       <c r="A354" s="3">
         <v>11</v>
       </c>
@@ -24952,8 +26026,11 @@
       <c r="V354" s="6"/>
       <c r="W354" s="6"/>
       <c r="X354" s="6"/>
-    </row>
-    <row r="355" spans="1:24" ht="15.75">
+      <c r="Y354" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="355" spans="1:25" ht="15.75">
       <c r="A355" s="3">
         <v>11</v>
       </c>
@@ -25019,8 +26096,11 @@
       <c r="V355" s="6"/>
       <c r="W355" s="6"/>
       <c r="X355" s="6"/>
-    </row>
-    <row r="356" spans="1:24" ht="15.75">
+      <c r="Y355" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="356" spans="1:25" ht="15.75">
       <c r="A356" s="3">
         <v>11</v>
       </c>
@@ -25086,8 +26166,11 @@
       <c r="V356" s="6"/>
       <c r="W356" s="6"/>
       <c r="X356" s="6"/>
-    </row>
-    <row r="357" spans="1:24" ht="15.75">
+      <c r="Y356" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="357" spans="1:25" ht="15.75">
       <c r="A357" s="3">
         <v>11</v>
       </c>
@@ -25153,8 +26236,11 @@
       <c r="V357" s="6"/>
       <c r="W357" s="6"/>
       <c r="X357" s="6"/>
-    </row>
-    <row r="358" spans="1:24" ht="15.75">
+      <c r="Y357" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="358" spans="1:25" ht="15.75">
       <c r="A358" s="3">
         <v>11</v>
       </c>
@@ -25220,8 +26306,11 @@
       <c r="V358" s="6"/>
       <c r="W358" s="6"/>
       <c r="X358" s="6"/>
-    </row>
-    <row r="359" spans="1:24" ht="15.75">
+      <c r="Y358" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="359" spans="1:25" ht="15.75">
       <c r="A359" s="3">
         <v>11</v>
       </c>
@@ -25287,8 +26376,11 @@
       <c r="V359" s="6"/>
       <c r="W359" s="6"/>
       <c r="X359" s="6"/>
-    </row>
-    <row r="360" spans="1:24" ht="15.75">
+      <c r="Y359" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="360" spans="1:25" ht="15.75">
       <c r="A360" s="3">
         <v>11</v>
       </c>
@@ -25360,8 +26452,11 @@
       <c r="X360" s="6">
         <v>0.70848</v>
       </c>
-    </row>
-    <row r="361" spans="1:24" ht="15.75">
+      <c r="Y360" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="361" spans="1:25" ht="15.75">
       <c r="A361" s="3">
         <v>11</v>
       </c>
@@ -25433,8 +26528,11 @@
       <c r="X361" s="6">
         <v>0.59367000000000003</v>
       </c>
-    </row>
-    <row r="362" spans="1:24" ht="15.75">
+      <c r="Y361" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="362" spans="1:25" ht="15.75">
       <c r="A362" s="3">
         <v>11</v>
       </c>
@@ -25506,8 +26604,11 @@
       <c r="X362" s="6">
         <v>0.49858000000000002</v>
       </c>
-    </row>
-    <row r="363" spans="1:24" ht="15.75">
+      <c r="Y362" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="363" spans="1:25" ht="15.75">
       <c r="A363" s="3">
         <v>11</v>
       </c>
@@ -25579,8 +26680,11 @@
       <c r="X363" s="6">
         <v>0.42049999999999998</v>
       </c>
-    </row>
-    <row r="364" spans="1:24" ht="15.75">
+      <c r="Y363" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="364" spans="1:25" ht="15.75">
       <c r="A364" s="3">
         <v>11</v>
       </c>
@@ -25652,8 +26756,11 @@
       <c r="X364" s="6">
         <v>0.35310999999999998</v>
       </c>
-    </row>
-    <row r="365" spans="1:24" ht="15.75">
+      <c r="Y364" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="365" spans="1:25" ht="15.75">
       <c r="A365" s="3">
         <v>11</v>
       </c>
@@ -25725,8 +26832,11 @@
       <c r="X365" s="6">
         <v>0.32372000000000001</v>
       </c>
-    </row>
-    <row r="366" spans="1:24" ht="15.75">
+      <c r="Y365" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="366" spans="1:25" ht="15.75">
       <c r="A366" s="3">
         <v>11</v>
       </c>
@@ -25798,8 +26908,11 @@
       <c r="X366" s="6">
         <v>0.27289999999999998</v>
       </c>
-    </row>
-    <row r="367" spans="1:24" ht="15.75">
+      <c r="Y366" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="367" spans="1:25" ht="15.75">
       <c r="A367" s="3">
         <v>11</v>
       </c>
@@ -25871,8 +26984,11 @@
       <c r="X367" s="6">
         <v>0.29726000000000002</v>
       </c>
-    </row>
-    <row r="368" spans="1:24" ht="15.75">
+      <c r="Y367" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="368" spans="1:25" ht="15.75">
       <c r="A368" s="3">
         <v>11</v>
       </c>
@@ -25944,8 +27060,11 @@
       <c r="X368" s="6">
         <v>0.24883</v>
       </c>
-    </row>
-    <row r="369" spans="1:24" ht="15.75">
+      <c r="Y368" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="369" spans="1:25" ht="15.75">
       <c r="A369" s="3">
         <v>11</v>
       </c>
@@ -26017,8 +27136,11 @@
       <c r="X369" s="6">
         <v>0.22925999999999999</v>
       </c>
-    </row>
-    <row r="370" spans="1:24" ht="15.75">
+      <c r="Y369" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="370" spans="1:25" ht="15.75">
       <c r="A370" s="3">
         <v>11</v>
       </c>
@@ -26090,8 +27212,11 @@
       <c r="X370" s="6">
         <v>0.21006</v>
       </c>
-    </row>
-    <row r="371" spans="1:24" ht="15.75">
+      <c r="Y370" s="13">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="371" spans="1:25" ht="15.75">
       <c r="A371" s="3">
         <v>11</v>
       </c>
@@ -26162,6 +27287,9 @@
       </c>
       <c r="X371" s="6">
         <v>0.17685000000000001</v>
+      </c>
+      <c r="Y371" s="13">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
